--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-09-06 05:26</t>
+          <t>Run: 2026-09-07 05:37</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-09-07 05:37</t>
+          <t>Run: 2026-09-08 05:33</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-09-13 05:36</t>
+          <t>Run: 2026-09-14 05:41</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W118"/>
+  <dimension ref="A1:W167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -705,37 +705,37 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>20260545869</t>
+          <t>20260548773</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Daniel Enriquez</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>KS StateBank</t>
-        </is>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="4" t="n">
-        <v>259000</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
+        <v>165000</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Maricopa County Courthouse</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>4201 N. 1 Avenue</t>
+          <t>1827 W EL MONTE PL</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>CHANDLER</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>85013</t>
+          <t>85224</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -758,12 +758,12 @@
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>156-45-184</t>
+          <t>302-89-734</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>Jessica A. Gale, Esq.</t>
+          <t>America West Lender Services, LLC</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>20260545931</t>
+          <t>20260548855</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MARIANNE GAWRONSKI-FISCHER</t>
+          <t>Omar Flores</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Onslow Bay Financial LLC</t>
+          <t>Metropolitan Financial Corp</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>325000</v>
+        <v>200000</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2045 S LA ROSA DR</t>
+          <t>3025 E Minton St</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>TEMPE</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>85282</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr"/>
@@ -859,12 +859,12 @@
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>133-25-064</t>
+          <t>102-09-250</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>MTC Financial Inc. dba Trustee Corps</t>
+          <t>Tolesoaz Corp. d/b/a Total Lender Solutions, an AZ Corp.</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -899,45 +899,45 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>20260546765</t>
+          <t>20260548873</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>an unmarried woman</t>
+          <t>BELLA UMALI GUTIERREZ</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4365 E Pecos Rd, Suite 108</t>
+          <t>ONSLOW BAY FINANCIAL LLC</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>238500</v>
+        <v>494600</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Court Building Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>11122 W Montana Ave.</t>
+          <t>2447 E HAZELTINE WAY</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Youngtown</t>
+          <t>GILBERT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>85363</t>
+          <t>85298</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
@@ -958,8 +958,16 @@
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>304-86-672</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>America West Lender Services, LL€</t>
+        </is>
+      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -992,49 +1000,57 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>20260546821</t>
+          <t>20260549116</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Eduardo Arguelles Landaverde</t>
+          <t>CARRIE M WILCOX-VAN TICHELT AND BRAD VAN TICHELT, WIFE AND HUSBAND AS</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Wilmington Trust, National Association as trustee for Current Trustee:</t>
+          <t>ROUNDPOINT MORTGAGE SERVICING LLC</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>208000</v>
+        <v>636000</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Superior Courts Building at the Maricopa County Courthouse</t>
+          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>16025 North Church Street</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>11423 N 12TH PL</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>85020</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
@@ -1043,14 +1059,10 @@
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>501-20-0425</t>
-        </is>
-      </c>
+      <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Tryon Street Acquisition Trust | Leonard J. McDonald</t>
+          <t>Prime Recon LLC</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1085,22 +1097,30 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>20260546978</t>
+          <t>20260549141</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>GERARDO MORENO AND LOURDES NAVARRO LEDESMA</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>TH MSR Holdings LLC</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="n">
-        <v>335000</v>
+        <v>318250</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1110,12 +1130,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>23639 W. Chickasaw St.</t>
+          <t>181 S 221ST DR</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Buckeye</t>
+          <t>BUCKEYE</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1138,10 +1158,14 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>504-28-367</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr"/>
+          <t>504-20-2980</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -1174,30 +1198,30 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>20260547170</t>
+          <t>20260549316</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Diane Cali</t>
+          <t>Susan Novak and Chad Novak</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>164000</v>
+        <v>276892</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1207,7 +1231,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>8437 W Audrey Ln</t>
+          <t>4156 W Michelle Dr</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
@@ -1227,12 +1251,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>233-04-2141</t>
+          <t>207-21-3370</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1267,57 +1291,45 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20260547731</t>
+          <t>20260549342</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>CHRISTEN BLANCHARD</t>
+          <t>Guy U Martinez and Natalie M Martinez</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>NEWREZ LLC D/B/A SHELLPOINT MORTGAGE SERVICING</t>
+          <t>U.S. Bank Trust Company National Association,, as Current Trustee:</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>455280</v>
+        <v>132600</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
-        </is>
-      </c>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>6721 S LAKESHORE DR</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>TEMPE</t>
-        </is>
-      </c>
+          <t>2658 West Naranja Avenue</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>85283</t>
-        </is>
-      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
@@ -1326,10 +1338,14 @@
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>305-04-6951</t>
+        </is>
+      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Prime Recon LLC</t>
+          <t>Indenture Trustee on behalf of and with respect to Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1349,684 +1365,744 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="A9" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>20260546069</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Roland Norman Prevost Jr</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Balboa LLC as to 20% beneficial interest</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>125000</v>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>2027-01-05</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>20260549383</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>MARYAM HCHAIMI</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>422211</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Superior Court Building</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr"/>
-      <c r="O9" s="7" t="inlineStr"/>
-      <c r="P9" s="7" t="inlineStr"/>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr"/>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>103-12-5491</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>' (</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>10650 N 49TH AVE</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>148-04-3585</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V9" s="7" t="inlineStr">
+      <c r="V9" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="A10" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>20260546723</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>MATTHEW P BESENFELDER</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Federal Home Loan Mortgage Corporation, as Trustee for Freddie Mac SLST 2022-2 Participation Interes</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>137144</v>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>2026-12-29</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Maricopa County Courthouse</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr"/>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr"/>
-      <c r="O10" s="7" t="inlineStr"/>
-      <c r="P10" s="7" t="inlineStr"/>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R10" s="7" t="inlineStr"/>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>301-05-229</t>
-        </is>
-      </c>
-      <c r="T10" s="7" t="inlineStr">
-        <is>
-          <t>Western Progressive — Arizona, Inc.</t>
-        </is>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>20260549876</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Osmyn Aaron Martinez</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>313500</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>5026 S 36th Ave</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>105-70-0908</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V10" s="7" t="inlineStr">
+      <c r="V10" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="A11" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>20260546866</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>C/O PNC Bank, N.A.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>140000</v>
-      </c>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>20260549877</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Kathreen Limin Canlas</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>312240</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>5518 W Glass Lane</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>104-91-3643</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>20260549906</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Elisabeth M. Weedman</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>105000</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>8800 N 107th Ave, Unit 64</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>142-72-6841</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>20260549911</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>DAVID DUNLAP AND SARA PHILLIPS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC sbm Nationstar Mortgage LLC</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>234000</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Superior Court Building</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr"/>
-      <c r="O11" s="7" t="inlineStr"/>
-      <c r="P11" s="7" t="inlineStr"/>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr"/>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>200-70-0151</t>
-        </is>
-      </c>
-      <c r="T11" s="7" t="inlineStr"/>
-      <c r="U11" s="7" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>629 W PLATAAVE</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>85210</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>302-77-598</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V11" s="7" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>20260547167</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Patrick Daniel Alexander</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>96000</v>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr"/>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>109 N Los Robles Dr</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr"/>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr"/>
-      <c r="O12" s="7" t="inlineStr"/>
-      <c r="P12" s="7" t="inlineStr"/>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr"/>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>500-15-1103</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>20260549913</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Michael W Johnson</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>244000</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>749 E Park Pl</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>138-23-032</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V12" s="7" t="inlineStr">
+      <c r="V14" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>20260547177</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Janet R. Miller</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>63741</v>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>1809 W Cheyenne Dr</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="7" t="inlineStr"/>
-      <c r="P13" s="7" t="inlineStr"/>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr"/>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>302-25-6970</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>20260549922</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Matthew James Hobbs and Christina M. Hobbs</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Alliant Credit Union Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>229000</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Superior Courts Building at the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>2810 West Windsong Drive</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>300-05-4289</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>Alliant Credit Union Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V13" s="7" t="inlineStr">
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>20260547526</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>WE Alliance Secured Income Fund, LLC</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>9052445</v>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr"/>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr"/>
-      <c r="O14" s="7" t="inlineStr"/>
-      <c r="P14" s="7" t="inlineStr"/>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R14" s="7" t="inlineStr"/>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>115-01-021</t>
-        </is>
-      </c>
-      <c r="T14" s="7" t="inlineStr">
-        <is>
-          <t>Christopher R. Perry, Esq.</t>
-        </is>
-      </c>
-      <c r="U14" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V14" s="7" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>20260549937</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Miami Real Estate Holdings</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Provident Trust Group FBO Theodore J Guarriello Jr Current Trustee:</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>461500</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Superior Courts Building at the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>1326 W Cove Drive</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>302-30-5338</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>IRA;Sandra_ Espinoza Guarriello;Theodore J. Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>20260547535</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>WE Alliance Secured Income Fund, LLC</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>9052445</v>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>115-01-021</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>Christopher R. Perry, Esq.</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>20260547549</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>C/O Planet Home Lending, LLC</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>327228</v>
-      </c>
-      <c r="I16" s="7" t="inlineStr"/>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr"/>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr"/>
-      <c r="P16" s="7" t="inlineStr"/>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr"/>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>140-38-072</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr"/>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -2034,7 +2110,7 @@
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -2048,24 +2124,32 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>20260546858</t>
+          <t>20260548175</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>BUDDY P. PEARCE AND ANGELA C. PEARCE</t>
+        </is>
+      </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>C/O JP MORGAN CHASE BANK- Milwaukee</t>
+          <t>HSBC Bank USA, N.A., as Trustee for the registered holders of First NLC Trust 2007-1 Mortgage-Backed</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I17" s="7" t="inlineStr"/>
+        <v>210000</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Superior Court Building</t>
@@ -2089,10 +2173,14 @@
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>102-82-039</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr"/>
+          <t>101-54-689</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2111,7 +2199,7 @@
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -2125,53 +2213,45 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>20260547776</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
+          <t>20260548742</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>ALICE H. RINK, A WIDOW</t>
+          <t>XIN WANG</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>NEWREZ LLC DBA SHELLPOINT MORTGAGE SERVICING</t>
+          <t>CSMC 2018-SP3 Trust</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>51563.8</v>
+        <v>292000</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>5548 N 9TH AVE</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
+          <t>Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>85013</t>
-        </is>
-      </c>
+      <c r="N18" s="7" t="inlineStr"/>
       <c r="O18" s="7" t="inlineStr"/>
       <c r="P18" s="7" t="inlineStr"/>
       <c r="Q18" s="7" t="inlineStr">
@@ -2180,15 +2260,19 @@
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr"/>
-      <c r="S18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>303-49-118</t>
+        </is>
+      </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>Prime Recon LLC</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
         <is>
-          <t>Pre-foreclosure; Trustee Sale</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V18" s="7" t="inlineStr">
@@ -2204,7 +2288,7 @@
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -2218,36 +2302,30 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>20260546721</t>
+          <t>20260549266</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>MICHAEL PAUL KAUFMAN AND MERYL LISA KAUFMAN</t>
-        </is>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>U.S. Bank Trust National Association, not in its individual capacity but solely as trustee on behalf</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr"/>
+          <t>C/O PNC Bank, N.A.</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>548250</v>
+      </c>
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>8830 W CORRINE DR</t>
-        </is>
-      </c>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr"/>
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr">
         <is>
@@ -2265,14 +2343,10 @@
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>200-79-930</t>
-        </is>
-      </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
+          <t>217-48-685</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr"/>
       <c r="U19" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2291,7 +2365,7 @@
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -2305,34 +2379,40 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>20260546849</t>
+          <t>20260549892</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>KIRK LOMAWAIMA</t>
+          <t>Martin Alday-Borjas</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>U.S. BANK TRUST NATIONAL ASSOCIATION, NOT IN ITS INDIVIDUAL CAPACITY BUT SOLELY</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
+          <t>Wells Fargo Bank, N.A. Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>73600</v>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>3526 WEST DUNLAP AVENUE UNIT 149</t>
+          <t>6222 S 2nd Ave</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr"/>
@@ -2352,12 +2432,12 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>149-39-515</t>
+          <t>114-03-0450</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Clear Recon Corp</t>
+          <t>Wells Fargo Bank, N.A. Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
@@ -2377,154 +2457,134 @@
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>20260546851</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr"/>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="7" t="inlineStr"/>
-      <c r="P21" s="7" t="inlineStr"/>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr"/>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>232-08-081</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr"/>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
+      <c r="A21" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>20260548552</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr"/>
+      <c r="G21" s="11" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr"/>
+      <c r="L21" s="11" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr"/>
+      <c r="O21" s="11" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr"/>
+      <c r="Q21" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="11" t="inlineStr"/>
+      <c r="S21" s="11" t="inlineStr"/>
+      <c r="T21" s="11" t="inlineStr"/>
+      <c r="U21" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="12" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="A22" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Probate Document</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>20260547657</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>4731 W Nicolet Ave.</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>85301</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr"/>
-      <c r="P22" s="7" t="inlineStr"/>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R22" s="7" t="inlineStr"/>
-      <c r="S22" s="7" t="inlineStr"/>
-      <c r="T22" s="7" t="inlineStr"/>
-      <c r="U22" s="7" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>20260548885</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr"/>
+      <c r="G22" s="11" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr"/>
+      <c r="I22" s="11" t="inlineStr"/>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT |</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr"/>
+      <c r="L22" s="11" t="inlineStr"/>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr"/>
+      <c r="O22" s="11" t="inlineStr"/>
+      <c r="P22" s="11" t="inlineStr"/>
+      <c r="Q22" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="11" t="inlineStr"/>
+      <c r="S22" s="11" t="inlineStr"/>
+      <c r="T22" s="11" t="inlineStr"/>
+      <c r="U22" s="11" t="inlineStr">
         <is>
           <t>Probate / estate; New this week</t>
         </is>
       </c>
-      <c r="V22" s="7" t="inlineStr">
+      <c r="V22" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="12" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -2532,38 +2592,38 @@
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>20260545780</t>
+          <t>20260548926</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr"/>
       <c r="H23" s="11" t="inlineStr"/>
       <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>13242 W LA TERRAZA DR</t>
-        </is>
-      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr"/>
       <c r="L23" s="11" t="inlineStr"/>
       <c r="M23" s="11" t="inlineStr">
         <is>
@@ -2583,7 +2643,7 @@
       <c r="T23" s="11" t="inlineStr"/>
       <c r="U23" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr">
@@ -2599,53 +2659,45 @@
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>20260547035</t>
+          <t>20260548995</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr"/>
       <c r="H24" s="11" t="inlineStr"/>
       <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>4036 W. Acoma Dr.</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>85053</t>
-        </is>
-      </c>
+      <c r="N24" s="11" t="inlineStr"/>
       <c r="O24" s="11" t="inlineStr"/>
       <c r="P24" s="11" t="inlineStr"/>
       <c r="Q24" s="11" t="inlineStr">
@@ -2658,7 +2710,7 @@
       <c r="T24" s="11" t="inlineStr"/>
       <c r="U24" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V24" s="11" t="inlineStr">
@@ -2674,53 +2726,45 @@
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>20260547036</t>
+          <t>20260549253</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr"/>
       <c r="G25" s="11" t="inlineStr"/>
       <c r="H25" s="11" t="inlineStr"/>
       <c r="I25" s="11" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>4202 W. Port Au Prince Ln.</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr"/>
+      <c r="L25" s="11" t="inlineStr"/>
       <c r="M25" s="11" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N25" s="11" t="inlineStr">
-        <is>
-          <t>85053</t>
-        </is>
-      </c>
+      <c r="N25" s="11" t="inlineStr"/>
       <c r="O25" s="11" t="inlineStr"/>
       <c r="P25" s="11" t="inlineStr"/>
       <c r="Q25" s="11" t="inlineStr">
@@ -2733,7 +2777,7 @@
       <c r="T25" s="11" t="inlineStr"/>
       <c r="U25" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V25" s="11" t="inlineStr">
@@ -2749,53 +2793,45 @@
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>20260547037</t>
+          <t>20260549533</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr"/>
       <c r="G26" s="11" t="inlineStr"/>
       <c r="H26" s="11" t="inlineStr"/>
       <c r="I26" s="11" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>4241 W. Monte Cristo Ave.</t>
-        </is>
-      </c>
-      <c r="L26" s="11" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr"/>
+      <c r="L26" s="11" t="inlineStr"/>
       <c r="M26" s="11" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N26" s="11" t="inlineStr">
-        <is>
-          <t>85053</t>
-        </is>
-      </c>
+      <c r="N26" s="11" t="inlineStr"/>
       <c r="O26" s="11" t="inlineStr"/>
       <c r="P26" s="11" t="inlineStr"/>
       <c r="Q26" s="11" t="inlineStr">
@@ -2808,7 +2844,7 @@
       <c r="T26" s="11" t="inlineStr"/>
       <c r="U26" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V26" s="11" t="inlineStr">
@@ -2828,22 +2864,22 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>20260545976</t>
+          <t>20260549782</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr"/>
@@ -2875,7 +2911,7 @@
       <c r="T27" s="11" t="inlineStr"/>
       <c r="U27" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr">
@@ -2895,22 +2931,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>20260547513</t>
+          <t>20260549835</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
@@ -2919,7 +2955,7 @@
       <c r="I28" s="11" t="inlineStr"/>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>SUPERIOR COURT</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -2942,7 +2978,7 @@
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V28" s="11" t="inlineStr">
@@ -2967,17 +3003,17 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>20260546374</t>
+          <t>20260550092</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
@@ -3025,37 +3061,33 @@
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>20260547174</t>
+          <t>20260549109</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="11" t="inlineStr"/>
       <c r="H30" s="11" t="inlineStr"/>
       <c r="I30" s="11" t="inlineStr"/>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr"/>
       <c r="L30" s="11" t="inlineStr"/>
       <c r="M30" s="11" t="inlineStr">
@@ -3076,7 +3108,7 @@
       <c r="T30" s="11" t="inlineStr"/>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V30" s="11" t="inlineStr">
@@ -3092,37 +3124,33 @@
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>20260547552</t>
+          <t>20260549124</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr"/>
       <c r="H31" s="11" t="inlineStr"/>
       <c r="I31" s="11" t="inlineStr"/>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr"/>
       <c r="L31" s="11" t="inlineStr"/>
       <c r="M31" s="11" t="inlineStr">
@@ -3143,7 +3171,7 @@
       <c r="T31" s="11" t="inlineStr"/>
       <c r="U31" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V31" s="11" t="inlineStr">
@@ -3159,37 +3187,33 @@
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>20260546379</t>
+          <t>20260549128</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
       <c r="G32" s="11" t="inlineStr"/>
       <c r="H32" s="11" t="inlineStr"/>
       <c r="I32" s="11" t="inlineStr"/>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr"/>
       <c r="L32" s="11" t="inlineStr"/>
       <c r="M32" s="11" t="inlineStr">
@@ -3210,7 +3234,7 @@
       <c r="T32" s="11" t="inlineStr"/>
       <c r="U32" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V32" s="11" t="inlineStr">
@@ -3226,37 +3250,33 @@
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>20260546555</t>
+          <t>20260549521</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr"/>
       <c r="H33" s="11" t="inlineStr"/>
       <c r="I33" s="11" t="inlineStr"/>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J33" s="11" t="inlineStr"/>
       <c r="K33" s="11" t="inlineStr"/>
       <c r="L33" s="11" t="inlineStr"/>
       <c r="M33" s="11" t="inlineStr">
@@ -3273,11 +3293,15 @@
         </is>
       </c>
       <c r="R33" s="11" t="inlineStr"/>
-      <c r="S33" s="11" t="inlineStr"/>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>312-17-010</t>
+        </is>
+      </c>
       <c r="T33" s="11" t="inlineStr"/>
       <c r="U33" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V33" s="11" t="inlineStr">
@@ -3293,37 +3317,33 @@
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>20260546653</t>
+          <t>20260549992</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
       <c r="G34" s="11" t="inlineStr"/>
       <c r="H34" s="11" t="inlineStr"/>
       <c r="I34" s="11" t="inlineStr"/>
-      <c r="J34" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr">
@@ -3344,7 +3364,7 @@
       <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V34" s="11" t="inlineStr">
@@ -3360,37 +3380,33 @@
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>20260546716</t>
+          <t>20260547881</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="inlineStr"/>
       <c r="H35" s="11" t="inlineStr"/>
       <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J35" s="11" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr"/>
       <c r="L35" s="11" t="inlineStr"/>
       <c r="M35" s="11" t="inlineStr">
@@ -3411,7 +3427,7 @@
       <c r="T35" s="11" t="inlineStr"/>
       <c r="U35" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V35" s="11" t="inlineStr">
@@ -3427,37 +3443,33 @@
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>20260546854</t>
+          <t>20260547882</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
       <c r="G36" s="11" t="inlineStr"/>
       <c r="H36" s="11" t="inlineStr"/>
       <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT ai</t>
-        </is>
-      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr">
@@ -3478,7 +3490,7 @@
       <c r="T36" s="11" t="inlineStr"/>
       <c r="U36" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V36" s="11" t="inlineStr">
@@ -3494,37 +3506,33 @@
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>20260547431</t>
+          <t>20260547883</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
       <c r="G37" s="11" t="inlineStr"/>
       <c r="H37" s="11" t="inlineStr"/>
       <c r="I37" s="11" t="inlineStr"/>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J37" s="11" t="inlineStr"/>
       <c r="K37" s="11" t="inlineStr"/>
       <c r="L37" s="11" t="inlineStr"/>
       <c r="M37" s="11" t="inlineStr">
@@ -3545,7 +3553,7 @@
       <c r="T37" s="11" t="inlineStr"/>
       <c r="U37" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V37" s="11" t="inlineStr">
@@ -3561,37 +3569,33 @@
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>20260547488</t>
+          <t>20260547884</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
       <c r="G38" s="11" t="inlineStr"/>
       <c r="H38" s="11" t="inlineStr"/>
       <c r="I38" s="11" t="inlineStr"/>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J38" s="11" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr"/>
       <c r="L38" s="11" t="inlineStr"/>
       <c r="M38" s="11" t="inlineStr">
@@ -3612,7 +3616,7 @@
       <c r="T38" s="11" t="inlineStr"/>
       <c r="U38" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V38" s="11" t="inlineStr">
@@ -3628,37 +3632,33 @@
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>20260547543</t>
+          <t>20260547885</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr"/>
       <c r="H39" s="11" t="inlineStr"/>
       <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J39" s="11" t="inlineStr"/>
       <c r="K39" s="11" t="inlineStr"/>
       <c r="L39" s="11" t="inlineStr"/>
       <c r="M39" s="11" t="inlineStr">
@@ -3679,7 +3679,7 @@
       <c r="T39" s="11" t="inlineStr"/>
       <c r="U39" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V39" s="11" t="inlineStr">
@@ -3699,22 +3699,22 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>20260546353</t>
+          <t>20260547886</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
@@ -3742,12 +3742,12 @@
       <c r="T40" s="11" t="inlineStr"/>
       <c r="U40" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V40" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W40" s="12" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>20260547748</t>
+          <t>20260547887</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
@@ -3805,12 +3805,12 @@
       <c r="T41" s="11" t="inlineStr"/>
       <c r="U41" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V41" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W41" s="12" t="inlineStr">
@@ -3825,22 +3825,22 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>20260547781</t>
+          <t>20260547888</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
@@ -3868,12 +3868,12 @@
       <c r="T42" s="11" t="inlineStr"/>
       <c r="U42" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V42" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W42" s="12" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>20260547854</t>
+          <t>20260547890</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
@@ -3931,12 +3931,12 @@
       <c r="T43" s="11" t="inlineStr"/>
       <c r="U43" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V43" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W43" s="12" t="inlineStr">
@@ -3947,26 +3947,26 @@
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>20260545421</t>
+          <t>20260547891</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
@@ -3994,7 +3994,7 @@
       <c r="T44" s="11" t="inlineStr"/>
       <c r="U44" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V44" s="11" t="inlineStr">
@@ -4010,26 +4010,26 @@
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>20260545422</t>
+          <t>20260547892</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       <c r="T45" s="11" t="inlineStr"/>
       <c r="U45" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V45" s="11" t="inlineStr">
@@ -4073,26 +4073,26 @@
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>20260545423</t>
+          <t>20260547893</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
@@ -4120,7 +4120,7 @@
       <c r="T46" s="11" t="inlineStr"/>
       <c r="U46" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V46" s="11" t="inlineStr">
@@ -4136,26 +4136,26 @@
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>20260545424</t>
+          <t>20260547894</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
@@ -4183,7 +4183,7 @@
       <c r="T47" s="11" t="inlineStr"/>
       <c r="U47" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V47" s="11" t="inlineStr">
@@ -4199,26 +4199,26 @@
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>20260545425</t>
+          <t>20260547895</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
@@ -4246,7 +4246,7 @@
       <c r="T48" s="11" t="inlineStr"/>
       <c r="U48" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V48" s="11" t="inlineStr">
@@ -4262,26 +4262,26 @@
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>20260545426</t>
+          <t>20260547896</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
@@ -4309,7 +4309,7 @@
       <c r="T49" s="11" t="inlineStr"/>
       <c r="U49" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V49" s="11" t="inlineStr">
@@ -4325,26 +4325,26 @@
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>20260545897</t>
+          <t>20260547897</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
@@ -4372,7 +4372,7 @@
       <c r="T50" s="11" t="inlineStr"/>
       <c r="U50" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V50" s="11" t="inlineStr">
@@ -4388,26 +4388,26 @@
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>20260545946</t>
+          <t>20260547898</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       <c r="T51" s="11" t="inlineStr"/>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
@@ -4451,26 +4451,26 @@
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>20260545947</t>
+          <t>20260547899</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
       <c r="T52" s="11" t="inlineStr"/>
       <c r="U52" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V52" s="11" t="inlineStr">
@@ -4514,26 +4514,26 @@
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>20260545948</t>
+          <t>20260547900</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
@@ -4561,7 +4561,7 @@
       <c r="T53" s="11" t="inlineStr"/>
       <c r="U53" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V53" s="11" t="inlineStr">
@@ -4577,26 +4577,26 @@
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>20260545949</t>
+          <t>20260547902</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
@@ -4624,7 +4624,7 @@
       <c r="T54" s="11" t="inlineStr"/>
       <c r="U54" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V54" s="11" t="inlineStr">
@@ -4640,26 +4640,26 @@
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>20260545950</t>
+          <t>20260547903</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
       <c r="T55" s="11" t="inlineStr"/>
       <c r="U55" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V55" s="11" t="inlineStr">
@@ -4703,26 +4703,26 @@
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>20260545958</t>
+          <t>20260547904</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
@@ -4750,7 +4750,7 @@
       <c r="T56" s="11" t="inlineStr"/>
       <c r="U56" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V56" s="11" t="inlineStr">
@@ -4766,26 +4766,26 @@
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>20260546105</t>
+          <t>20260547906</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
       <c r="T57" s="11" t="inlineStr"/>
       <c r="U57" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V57" s="11" t="inlineStr">
@@ -4829,26 +4829,26 @@
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>20260546136</t>
+          <t>20260547907</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
@@ -4876,7 +4876,7 @@
       <c r="T58" s="11" t="inlineStr"/>
       <c r="U58" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V58" s="11" t="inlineStr">
@@ -4892,26 +4892,26 @@
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>20260546137</t>
+          <t>20260547908</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
@@ -4939,7 +4939,7 @@
       <c r="T59" s="11" t="inlineStr"/>
       <c r="U59" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V59" s="11" t="inlineStr">
@@ -4955,26 +4955,26 @@
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>20260546207</t>
+          <t>20260547909</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
@@ -5002,7 +5002,7 @@
       <c r="T60" s="11" t="inlineStr"/>
       <c r="U60" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V60" s="11" t="inlineStr">
@@ -5018,26 +5018,26 @@
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>20260546208</t>
+          <t>20260547910</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -5065,7 +5065,7 @@
       <c r="T61" s="11" t="inlineStr"/>
       <c r="U61" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V61" s="11" t="inlineStr">
@@ -5081,26 +5081,26 @@
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>20260546362</t>
+          <t>20260547986</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
       <c r="T62" s="11" t="inlineStr"/>
       <c r="U62" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V62" s="11" t="inlineStr">
@@ -5144,26 +5144,26 @@
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>20260546422</t>
+          <t>20260547988</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
@@ -5191,7 +5191,7 @@
       <c r="T63" s="11" t="inlineStr"/>
       <c r="U63" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V63" s="11" t="inlineStr">
@@ -5207,26 +5207,26 @@
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>20260546616</t>
+          <t>20260548086</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
       <c r="T64" s="11" t="inlineStr"/>
       <c r="U64" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V64" s="11" t="inlineStr">
@@ -5270,26 +5270,26 @@
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>20260546617</t>
+          <t>20260548087</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -5317,7 +5317,7 @@
       <c r="T65" s="11" t="inlineStr"/>
       <c r="U65" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V65" s="11" t="inlineStr">
@@ -5333,26 +5333,26 @@
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>20260546622</t>
+          <t>20260548088</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
@@ -5380,7 +5380,7 @@
       <c r="T66" s="11" t="inlineStr"/>
       <c r="U66" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V66" s="11" t="inlineStr">
@@ -5396,26 +5396,26 @@
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>20260546623</t>
+          <t>20260548089</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
@@ -5443,7 +5443,7 @@
       <c r="T67" s="11" t="inlineStr"/>
       <c r="U67" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V67" s="11" t="inlineStr">
@@ -5459,26 +5459,26 @@
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>20260546624</t>
+          <t>20260548090</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -5506,7 +5506,7 @@
       <c r="T68" s="11" t="inlineStr"/>
       <c r="U68" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V68" s="11" t="inlineStr">
@@ -5522,26 +5522,26 @@
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>20260546625</t>
+          <t>20260548091</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
@@ -5569,7 +5569,7 @@
       <c r="T69" s="11" t="inlineStr"/>
       <c r="U69" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V69" s="11" t="inlineStr">
@@ -5585,26 +5585,26 @@
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>20260546626</t>
+          <t>20260548092</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
       <c r="T70" s="11" t="inlineStr"/>
       <c r="U70" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V70" s="11" t="inlineStr">
@@ -5648,26 +5648,26 @@
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>20260546627</t>
+          <t>20260548096</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
@@ -5695,7 +5695,7 @@
       <c r="T71" s="11" t="inlineStr"/>
       <c r="U71" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V71" s="11" t="inlineStr">
@@ -5711,26 +5711,26 @@
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>20260546637</t>
+          <t>20260548097</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       <c r="T72" s="11" t="inlineStr"/>
       <c r="U72" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V72" s="11" t="inlineStr">
@@ -5774,26 +5774,26 @@
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>20260546642</t>
+          <t>20260548185</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
@@ -5821,7 +5821,7 @@
       <c r="T73" s="11" t="inlineStr"/>
       <c r="U73" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V73" s="11" t="inlineStr">
@@ -5837,26 +5837,26 @@
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>20260546643</t>
+          <t>20260548187</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -5884,7 +5884,7 @@
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
@@ -5900,26 +5900,26 @@
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>20260546644</t>
+          <t>20260548188</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
@@ -5947,7 +5947,7 @@
       <c r="T75" s="11" t="inlineStr"/>
       <c r="U75" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V75" s="11" t="inlineStr">
@@ -5963,26 +5963,26 @@
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>20260546645</t>
+          <t>20260548192</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
@@ -6010,7 +6010,7 @@
       <c r="T76" s="11" t="inlineStr"/>
       <c r="U76" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V76" s="11" t="inlineStr">
@@ -6026,26 +6026,26 @@
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>20260546646</t>
+          <t>20260548210</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr"/>
@@ -6073,7 +6073,7 @@
       <c r="T77" s="11" t="inlineStr"/>
       <c r="U77" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V77" s="11" t="inlineStr">
@@ -6089,26 +6089,26 @@
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>20260546647</t>
+          <t>20260548304</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -6136,7 +6136,7 @@
       <c r="T78" s="11" t="inlineStr"/>
       <c r="U78" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V78" s="11" t="inlineStr">
@@ -6152,26 +6152,26 @@
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>20260546648</t>
+          <t>20260548470</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
@@ -6199,7 +6199,7 @@
       <c r="T79" s="11" t="inlineStr"/>
       <c r="U79" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V79" s="11" t="inlineStr">
@@ -6215,26 +6215,26 @@
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>20260546657</t>
+          <t>20260548597</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
@@ -6262,7 +6262,7 @@
       <c r="T80" s="11" t="inlineStr"/>
       <c r="U80" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V80" s="11" t="inlineStr">
@@ -6278,26 +6278,26 @@
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>20260546659</t>
+          <t>20260548598</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
       <c r="T81" s="11" t="inlineStr"/>
       <c r="U81" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V81" s="11" t="inlineStr">
@@ -6341,26 +6341,26 @@
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>20260546660</t>
+          <t>20260548600</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
@@ -6388,7 +6388,7 @@
       <c r="T82" s="11" t="inlineStr"/>
       <c r="U82" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V82" s="11" t="inlineStr">
@@ -6404,26 +6404,26 @@
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>20260546661</t>
+          <t>20260548601</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       <c r="T83" s="11" t="inlineStr"/>
       <c r="U83" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V83" s="11" t="inlineStr">
@@ -6467,26 +6467,26 @@
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>20260546662</t>
+          <t>20260548606</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
@@ -6514,7 +6514,7 @@
       <c r="T84" s="11" t="inlineStr"/>
       <c r="U84" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V84" s="11" t="inlineStr">
@@ -6530,26 +6530,26 @@
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>20260546663</t>
+          <t>20260548607</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
@@ -6577,7 +6577,7 @@
       <c r="T85" s="11" t="inlineStr"/>
       <c r="U85" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V85" s="11" t="inlineStr">
@@ -6593,26 +6593,26 @@
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>20260546664</t>
+          <t>20260548608</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
@@ -6640,7 +6640,7 @@
       <c r="T86" s="11" t="inlineStr"/>
       <c r="U86" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V86" s="11" t="inlineStr">
@@ -6656,26 +6656,26 @@
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>20260546665</t>
+          <t>20260548609</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
@@ -6703,7 +6703,7 @@
       <c r="T87" s="11" t="inlineStr"/>
       <c r="U87" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V87" s="11" t="inlineStr">
@@ -6719,26 +6719,26 @@
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>20260546666</t>
+          <t>20260548610</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
@@ -6766,7 +6766,7 @@
       <c r="T88" s="11" t="inlineStr"/>
       <c r="U88" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V88" s="11" t="inlineStr">
@@ -6782,26 +6782,26 @@
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>20260546667</t>
+          <t>20260548611</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
@@ -6829,7 +6829,7 @@
       <c r="T89" s="11" t="inlineStr"/>
       <c r="U89" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V89" s="11" t="inlineStr">
@@ -6845,26 +6845,26 @@
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>20260546668</t>
+          <t>20260548612</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -6892,7 +6892,7 @@
       <c r="T90" s="11" t="inlineStr"/>
       <c r="U90" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V90" s="11" t="inlineStr">
@@ -6908,26 +6908,26 @@
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>20260546669</t>
+          <t>20260548613</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
@@ -6955,7 +6955,7 @@
       <c r="T91" s="11" t="inlineStr"/>
       <c r="U91" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V91" s="11" t="inlineStr">
@@ -6971,26 +6971,26 @@
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>20260546670</t>
+          <t>20260550338</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       <c r="T92" s="11" t="inlineStr"/>
       <c r="U92" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V92" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W92" s="12" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>20260546671</t>
+          <t>20260548525</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>20260546672</t>
+          <t>20260548526</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr"/>
@@ -7174,12 +7174,12 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>20260546674</t>
+          <t>20260548527</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>20260546677</t>
+          <t>20260548528</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr"/>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>20260546684</t>
+          <t>20260548529</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
@@ -7363,12 +7363,12 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>20260546687</t>
+          <t>20260548530</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr"/>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>20260546688</t>
+          <t>20260548531</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>20260546695</t>
+          <t>20260548754</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
@@ -7552,12 +7552,12 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>20260546747</t>
+          <t>20260548789</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr"/>
@@ -7581,7 +7581,11 @@
         </is>
       </c>
       <c r="R101" s="11" t="inlineStr"/>
-      <c r="S101" s="11" t="inlineStr"/>
+      <c r="S101" s="11" t="inlineStr">
+        <is>
+          <t>123-18-5734479</t>
+        </is>
+      </c>
       <c r="T101" s="11" t="inlineStr"/>
       <c r="U101" s="11" t="inlineStr">
         <is>
@@ -7615,12 +7619,12 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>20260546750</t>
+          <t>20260548824</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr"/>
@@ -7678,12 +7682,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>20260546812</t>
+          <t>20260548829</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr"/>
@@ -7741,12 +7745,12 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>20260546813</t>
+          <t>20260548838</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr"/>
@@ -7804,12 +7808,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>20260546816</t>
+          <t>20260548849</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr"/>
@@ -7867,12 +7871,12 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>20260546829</t>
+          <t>20260549241</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr"/>
@@ -7930,12 +7934,12 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>20260546862</t>
+          <t>20260549752</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
@@ -7993,12 +7997,12 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>20260546903</t>
+          <t>20260549759</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr"/>
@@ -8056,12 +8060,12 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>20260546913</t>
+          <t>20260549767</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr"/>
@@ -8119,12 +8123,12 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>20260546938</t>
+          <t>20260549768</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr"/>
@@ -8182,12 +8186,12 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>20260547833</t>
+          <t>20260549771</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr"/>
@@ -8245,12 +8249,12 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>20260547834</t>
+          <t>20260550151</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -8294,26 +8298,26 @@
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>20260547838</t>
+          <t>20260548682</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr"/>
@@ -8341,12 +8345,12 @@
       <c r="T113" s="11" t="inlineStr"/>
       <c r="U113" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V113" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W113" s="12" t="inlineStr">
@@ -8357,26 +8361,26 @@
     </row>
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>20260547839</t>
+          <t>20260548690</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
@@ -8404,12 +8408,12 @@
       <c r="T114" s="11" t="inlineStr"/>
       <c r="U114" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V114" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W114" s="12" t="inlineStr">
@@ -8420,26 +8424,26 @@
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>20260547841</t>
+          <t>20260548691</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr"/>
@@ -8467,12 +8471,12 @@
       <c r="T115" s="11" t="inlineStr"/>
       <c r="U115" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V115" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W115" s="12" t="inlineStr">
@@ -8483,26 +8487,26 @@
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>20260547844</t>
+          <t>20260548714</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr"/>
@@ -8530,12 +8534,12 @@
       <c r="T116" s="11" t="inlineStr"/>
       <c r="U116" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V116" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W116" s="12" t="inlineStr">
@@ -8546,26 +8550,26 @@
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>20260547845</t>
+          <t>20260548799</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr"/>
@@ -8593,12 +8597,12 @@
       <c r="T117" s="11" t="inlineStr"/>
       <c r="U117" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V117" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W117" s="12" t="inlineStr">
@@ -8609,26 +8613,26 @@
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>20260547846</t>
+          <t>20260548820</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
@@ -8656,12 +8660,12 @@
       <c r="T118" s="11" t="inlineStr"/>
       <c r="U118" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V118" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W118" s="12" t="inlineStr">
@@ -8670,8 +8674,3095 @@
         </is>
       </c>
     </row>
+    <row r="119" ht="26" customHeight="1">
+      <c r="A119" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>20260548929</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr"/>
+      <c r="G119" s="11" t="inlineStr"/>
+      <c r="H119" s="11" t="inlineStr"/>
+      <c r="I119" s="11" t="inlineStr"/>
+      <c r="J119" s="11" t="inlineStr"/>
+      <c r="K119" s="11" t="inlineStr"/>
+      <c r="L119" s="11" t="inlineStr"/>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N119" s="11" t="inlineStr"/>
+      <c r="O119" s="11" t="inlineStr"/>
+      <c r="P119" s="11" t="inlineStr"/>
+      <c r="Q119" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R119" s="11" t="inlineStr"/>
+      <c r="S119" s="11" t="inlineStr"/>
+      <c r="T119" s="11" t="inlineStr"/>
+      <c r="U119" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V119" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W119" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="26" customHeight="1">
+      <c r="A120" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>20260548937</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr"/>
+      <c r="G120" s="11" t="inlineStr"/>
+      <c r="H120" s="11" t="inlineStr"/>
+      <c r="I120" s="11" t="inlineStr"/>
+      <c r="J120" s="11" t="inlineStr"/>
+      <c r="K120" s="11" t="inlineStr"/>
+      <c r="L120" s="11" t="inlineStr"/>
+      <c r="M120" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N120" s="11" t="inlineStr"/>
+      <c r="O120" s="11" t="inlineStr"/>
+      <c r="P120" s="11" t="inlineStr"/>
+      <c r="Q120" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R120" s="11" t="inlineStr"/>
+      <c r="S120" s="11" t="inlineStr"/>
+      <c r="T120" s="11" t="inlineStr"/>
+      <c r="U120" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V120" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W120" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="26" customHeight="1">
+      <c r="A121" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>20260548938</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr"/>
+      <c r="G121" s="11" t="inlineStr"/>
+      <c r="H121" s="11" t="inlineStr"/>
+      <c r="I121" s="11" t="inlineStr"/>
+      <c r="J121" s="11" t="inlineStr"/>
+      <c r="K121" s="11" t="inlineStr"/>
+      <c r="L121" s="11" t="inlineStr"/>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N121" s="11" t="inlineStr"/>
+      <c r="O121" s="11" t="inlineStr"/>
+      <c r="P121" s="11" t="inlineStr"/>
+      <c r="Q121" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R121" s="11" t="inlineStr"/>
+      <c r="S121" s="11" t="inlineStr"/>
+      <c r="T121" s="11" t="inlineStr"/>
+      <c r="U121" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V121" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W121" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="26" customHeight="1">
+      <c r="A122" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>20260548969</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr"/>
+      <c r="G122" s="11" t="inlineStr"/>
+      <c r="H122" s="11" t="inlineStr"/>
+      <c r="I122" s="11" t="inlineStr"/>
+      <c r="J122" s="11" t="inlineStr"/>
+      <c r="K122" s="11" t="inlineStr"/>
+      <c r="L122" s="11" t="inlineStr"/>
+      <c r="M122" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N122" s="11" t="inlineStr"/>
+      <c r="O122" s="11" t="inlineStr"/>
+      <c r="P122" s="11" t="inlineStr"/>
+      <c r="Q122" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R122" s="11" t="inlineStr"/>
+      <c r="S122" s="11" t="inlineStr"/>
+      <c r="T122" s="11" t="inlineStr"/>
+      <c r="U122" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V122" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W122" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="26" customHeight="1">
+      <c r="A123" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>20260549014</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr"/>
+      <c r="G123" s="11" t="inlineStr"/>
+      <c r="H123" s="11" t="inlineStr"/>
+      <c r="I123" s="11" t="inlineStr"/>
+      <c r="J123" s="11" t="inlineStr"/>
+      <c r="K123" s="11" t="inlineStr"/>
+      <c r="L123" s="11" t="inlineStr"/>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N123" s="11" t="inlineStr"/>
+      <c r="O123" s="11" t="inlineStr"/>
+      <c r="P123" s="11" t="inlineStr"/>
+      <c r="Q123" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R123" s="11" t="inlineStr"/>
+      <c r="S123" s="11" t="inlineStr"/>
+      <c r="T123" s="11" t="inlineStr"/>
+      <c r="U123" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V123" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W123" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="26" customHeight="1">
+      <c r="A124" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>20260549015</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr"/>
+      <c r="G124" s="11" t="inlineStr"/>
+      <c r="H124" s="11" t="inlineStr"/>
+      <c r="I124" s="11" t="inlineStr"/>
+      <c r="J124" s="11" t="inlineStr"/>
+      <c r="K124" s="11" t="inlineStr"/>
+      <c r="L124" s="11" t="inlineStr"/>
+      <c r="M124" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N124" s="11" t="inlineStr"/>
+      <c r="O124" s="11" t="inlineStr"/>
+      <c r="P124" s="11" t="inlineStr"/>
+      <c r="Q124" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R124" s="11" t="inlineStr"/>
+      <c r="S124" s="11" t="inlineStr"/>
+      <c r="T124" s="11" t="inlineStr"/>
+      <c r="U124" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V124" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W124" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="26" customHeight="1">
+      <c r="A125" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>20260549016</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr"/>
+      <c r="G125" s="11" t="inlineStr"/>
+      <c r="H125" s="11" t="inlineStr"/>
+      <c r="I125" s="11" t="inlineStr"/>
+      <c r="J125" s="11" t="inlineStr"/>
+      <c r="K125" s="11" t="inlineStr"/>
+      <c r="L125" s="11" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N125" s="11" t="inlineStr"/>
+      <c r="O125" s="11" t="inlineStr"/>
+      <c r="P125" s="11" t="inlineStr"/>
+      <c r="Q125" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R125" s="11" t="inlineStr"/>
+      <c r="S125" s="11" t="inlineStr"/>
+      <c r="T125" s="11" t="inlineStr"/>
+      <c r="U125" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V125" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W125" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="26" customHeight="1">
+      <c r="A126" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>20260549022</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr"/>
+      <c r="G126" s="11" t="inlineStr"/>
+      <c r="H126" s="11" t="inlineStr"/>
+      <c r="I126" s="11" t="inlineStr"/>
+      <c r="J126" s="11" t="inlineStr"/>
+      <c r="K126" s="11" t="inlineStr"/>
+      <c r="L126" s="11" t="inlineStr"/>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N126" s="11" t="inlineStr"/>
+      <c r="O126" s="11" t="inlineStr"/>
+      <c r="P126" s="11" t="inlineStr"/>
+      <c r="Q126" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R126" s="11" t="inlineStr"/>
+      <c r="S126" s="11" t="inlineStr"/>
+      <c r="T126" s="11" t="inlineStr"/>
+      <c r="U126" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V126" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W126" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="26" customHeight="1">
+      <c r="A127" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>20260549044</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr"/>
+      <c r="G127" s="11" t="inlineStr"/>
+      <c r="H127" s="11" t="inlineStr"/>
+      <c r="I127" s="11" t="inlineStr"/>
+      <c r="J127" s="11" t="inlineStr"/>
+      <c r="K127" s="11" t="inlineStr"/>
+      <c r="L127" s="11" t="inlineStr"/>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N127" s="11" t="inlineStr"/>
+      <c r="O127" s="11" t="inlineStr"/>
+      <c r="P127" s="11" t="inlineStr"/>
+      <c r="Q127" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R127" s="11" t="inlineStr"/>
+      <c r="S127" s="11" t="inlineStr"/>
+      <c r="T127" s="11" t="inlineStr"/>
+      <c r="U127" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V127" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W127" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="26" customHeight="1">
+      <c r="A128" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>20260549097</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr"/>
+      <c r="G128" s="11" t="inlineStr"/>
+      <c r="H128" s="11" t="inlineStr"/>
+      <c r="I128" s="11" t="inlineStr"/>
+      <c r="J128" s="11" t="inlineStr"/>
+      <c r="K128" s="11" t="inlineStr"/>
+      <c r="L128" s="11" t="inlineStr"/>
+      <c r="M128" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N128" s="11" t="inlineStr"/>
+      <c r="O128" s="11" t="inlineStr"/>
+      <c r="P128" s="11" t="inlineStr"/>
+      <c r="Q128" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R128" s="11" t="inlineStr"/>
+      <c r="S128" s="11" t="inlineStr"/>
+      <c r="T128" s="11" t="inlineStr"/>
+      <c r="U128" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V128" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W128" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="26" customHeight="1">
+      <c r="A129" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>20260549165</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr"/>
+      <c r="G129" s="11" t="inlineStr"/>
+      <c r="H129" s="11" t="inlineStr"/>
+      <c r="I129" s="11" t="inlineStr"/>
+      <c r="J129" s="11" t="inlineStr"/>
+      <c r="K129" s="11" t="inlineStr"/>
+      <c r="L129" s="11" t="inlineStr"/>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N129" s="11" t="inlineStr"/>
+      <c r="O129" s="11" t="inlineStr"/>
+      <c r="P129" s="11" t="inlineStr"/>
+      <c r="Q129" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R129" s="11" t="inlineStr"/>
+      <c r="S129" s="11" t="inlineStr"/>
+      <c r="T129" s="11" t="inlineStr"/>
+      <c r="U129" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V129" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W129" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="26" customHeight="1">
+      <c r="A130" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>20260549354</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr"/>
+      <c r="G130" s="11" t="inlineStr"/>
+      <c r="H130" s="11" t="inlineStr"/>
+      <c r="I130" s="11" t="inlineStr"/>
+      <c r="J130" s="11" t="inlineStr"/>
+      <c r="K130" s="11" t="inlineStr"/>
+      <c r="L130" s="11" t="inlineStr"/>
+      <c r="M130" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N130" s="11" t="inlineStr"/>
+      <c r="O130" s="11" t="inlineStr"/>
+      <c r="P130" s="11" t="inlineStr"/>
+      <c r="Q130" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R130" s="11" t="inlineStr"/>
+      <c r="S130" s="11" t="inlineStr"/>
+      <c r="T130" s="11" t="inlineStr"/>
+      <c r="U130" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V130" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W130" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="26" customHeight="1">
+      <c r="A131" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>20260549365</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr"/>
+      <c r="G131" s="11" t="inlineStr"/>
+      <c r="H131" s="11" t="inlineStr"/>
+      <c r="I131" s="11" t="inlineStr"/>
+      <c r="J131" s="11" t="inlineStr"/>
+      <c r="K131" s="11" t="inlineStr"/>
+      <c r="L131" s="11" t="inlineStr"/>
+      <c r="M131" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N131" s="11" t="inlineStr"/>
+      <c r="O131" s="11" t="inlineStr"/>
+      <c r="P131" s="11" t="inlineStr"/>
+      <c r="Q131" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R131" s="11" t="inlineStr"/>
+      <c r="S131" s="11" t="inlineStr"/>
+      <c r="T131" s="11" t="inlineStr"/>
+      <c r="U131" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V131" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W131" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="26" customHeight="1">
+      <c r="A132" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>20260549370</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr"/>
+      <c r="G132" s="11" t="inlineStr"/>
+      <c r="H132" s="11" t="inlineStr"/>
+      <c r="I132" s="11" t="inlineStr"/>
+      <c r="J132" s="11" t="inlineStr"/>
+      <c r="K132" s="11" t="inlineStr"/>
+      <c r="L132" s="11" t="inlineStr"/>
+      <c r="M132" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N132" s="11" t="inlineStr"/>
+      <c r="O132" s="11" t="inlineStr"/>
+      <c r="P132" s="11" t="inlineStr"/>
+      <c r="Q132" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R132" s="11" t="inlineStr"/>
+      <c r="S132" s="11" t="inlineStr"/>
+      <c r="T132" s="11" t="inlineStr"/>
+      <c r="U132" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V132" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W132" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="26" customHeight="1">
+      <c r="A133" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>20260549371</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr"/>
+      <c r="G133" s="11" t="inlineStr"/>
+      <c r="H133" s="11" t="inlineStr"/>
+      <c r="I133" s="11" t="inlineStr"/>
+      <c r="J133" s="11" t="inlineStr"/>
+      <c r="K133" s="11" t="inlineStr"/>
+      <c r="L133" s="11" t="inlineStr"/>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N133" s="11" t="inlineStr"/>
+      <c r="O133" s="11" t="inlineStr"/>
+      <c r="P133" s="11" t="inlineStr"/>
+      <c r="Q133" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R133" s="11" t="inlineStr"/>
+      <c r="S133" s="11" t="inlineStr"/>
+      <c r="T133" s="11" t="inlineStr"/>
+      <c r="U133" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V133" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W133" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="26" customHeight="1">
+      <c r="A134" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>20260549376</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr"/>
+      <c r="G134" s="11" t="inlineStr"/>
+      <c r="H134" s="11" t="inlineStr"/>
+      <c r="I134" s="11" t="inlineStr"/>
+      <c r="J134" s="11" t="inlineStr"/>
+      <c r="K134" s="11" t="inlineStr"/>
+      <c r="L134" s="11" t="inlineStr"/>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N134" s="11" t="inlineStr"/>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr"/>
+      <c r="Q134" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R134" s="11" t="inlineStr"/>
+      <c r="S134" s="11" t="inlineStr"/>
+      <c r="T134" s="11" t="inlineStr"/>
+      <c r="U134" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V134" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W134" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="26" customHeight="1">
+      <c r="A135" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>20260549407</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr"/>
+      <c r="G135" s="11" t="inlineStr"/>
+      <c r="H135" s="11" t="inlineStr"/>
+      <c r="I135" s="11" t="inlineStr"/>
+      <c r="J135" s="11" t="inlineStr"/>
+      <c r="K135" s="11" t="inlineStr"/>
+      <c r="L135" s="11" t="inlineStr"/>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N135" s="11" t="inlineStr"/>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="11" t="inlineStr"/>
+      <c r="Q135" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R135" s="11" t="inlineStr"/>
+      <c r="S135" s="11" t="inlineStr"/>
+      <c r="T135" s="11" t="inlineStr"/>
+      <c r="U135" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V135" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W135" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="26" customHeight="1">
+      <c r="A136" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>20260549423</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr"/>
+      <c r="G136" s="11" t="inlineStr"/>
+      <c r="H136" s="11" t="inlineStr"/>
+      <c r="I136" s="11" t="inlineStr"/>
+      <c r="J136" s="11" t="inlineStr"/>
+      <c r="K136" s="11" t="inlineStr"/>
+      <c r="L136" s="11" t="inlineStr"/>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N136" s="11" t="inlineStr"/>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="11" t="inlineStr"/>
+      <c r="Q136" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R136" s="11" t="inlineStr"/>
+      <c r="S136" s="11" t="inlineStr"/>
+      <c r="T136" s="11" t="inlineStr"/>
+      <c r="U136" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V136" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W136" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="26" customHeight="1">
+      <c r="A137" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>20260549442</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr"/>
+      <c r="G137" s="11" t="inlineStr"/>
+      <c r="H137" s="11" t="inlineStr"/>
+      <c r="I137" s="11" t="inlineStr"/>
+      <c r="J137" s="11" t="inlineStr"/>
+      <c r="K137" s="11" t="inlineStr"/>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N137" s="11" t="inlineStr"/>
+      <c r="O137" s="11" t="inlineStr"/>
+      <c r="P137" s="11" t="inlineStr"/>
+      <c r="Q137" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R137" s="11" t="inlineStr"/>
+      <c r="S137" s="11" t="inlineStr"/>
+      <c r="T137" s="11" t="inlineStr"/>
+      <c r="U137" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V137" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W137" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="26" customHeight="1">
+      <c r="A138" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>20260549464</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr"/>
+      <c r="G138" s="11" t="inlineStr"/>
+      <c r="H138" s="11" t="inlineStr"/>
+      <c r="I138" s="11" t="inlineStr"/>
+      <c r="J138" s="11" t="inlineStr"/>
+      <c r="K138" s="11" t="inlineStr"/>
+      <c r="L138" s="11" t="inlineStr"/>
+      <c r="M138" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N138" s="11" t="inlineStr"/>
+      <c r="O138" s="11" t="inlineStr"/>
+      <c r="P138" s="11" t="inlineStr"/>
+      <c r="Q138" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R138" s="11" t="inlineStr"/>
+      <c r="S138" s="11" t="inlineStr"/>
+      <c r="T138" s="11" t="inlineStr"/>
+      <c r="U138" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V138" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W138" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="26" customHeight="1">
+      <c r="A139" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>20260549477</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr"/>
+      <c r="G139" s="11" t="inlineStr"/>
+      <c r="H139" s="11" t="inlineStr"/>
+      <c r="I139" s="11" t="inlineStr"/>
+      <c r="J139" s="11" t="inlineStr"/>
+      <c r="K139" s="11" t="inlineStr"/>
+      <c r="L139" s="11" t="inlineStr"/>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N139" s="11" t="inlineStr"/>
+      <c r="O139" s="11" t="inlineStr"/>
+      <c r="P139" s="11" t="inlineStr"/>
+      <c r="Q139" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R139" s="11" t="inlineStr"/>
+      <c r="S139" s="11" t="inlineStr"/>
+      <c r="T139" s="11" t="inlineStr"/>
+      <c r="U139" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V139" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W139" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="26" customHeight="1">
+      <c r="A140" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>20260549497</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr"/>
+      <c r="G140" s="11" t="inlineStr"/>
+      <c r="H140" s="11" t="inlineStr"/>
+      <c r="I140" s="11" t="inlineStr"/>
+      <c r="J140" s="11" t="inlineStr"/>
+      <c r="K140" s="11" t="inlineStr"/>
+      <c r="L140" s="11" t="inlineStr"/>
+      <c r="M140" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N140" s="11" t="inlineStr"/>
+      <c r="O140" s="11" t="inlineStr"/>
+      <c r="P140" s="11" t="inlineStr"/>
+      <c r="Q140" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R140" s="11" t="inlineStr"/>
+      <c r="S140" s="11" t="inlineStr"/>
+      <c r="T140" s="11" t="inlineStr"/>
+      <c r="U140" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V140" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W140" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="26" customHeight="1">
+      <c r="A141" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>20260549516</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr"/>
+      <c r="G141" s="11" t="inlineStr"/>
+      <c r="H141" s="11" t="inlineStr"/>
+      <c r="I141" s="11" t="inlineStr"/>
+      <c r="J141" s="11" t="inlineStr"/>
+      <c r="K141" s="11" t="inlineStr"/>
+      <c r="L141" s="11" t="inlineStr"/>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N141" s="11" t="inlineStr"/>
+      <c r="O141" s="11" t="inlineStr"/>
+      <c r="P141" s="11" t="inlineStr"/>
+      <c r="Q141" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R141" s="11" t="inlineStr"/>
+      <c r="S141" s="11" t="inlineStr"/>
+      <c r="T141" s="11" t="inlineStr"/>
+      <c r="U141" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V141" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W141" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="26" customHeight="1">
+      <c r="A142" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>20260549953</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr"/>
+      <c r="G142" s="11" t="inlineStr"/>
+      <c r="H142" s="11" t="inlineStr"/>
+      <c r="I142" s="11" t="inlineStr"/>
+      <c r="J142" s="11" t="inlineStr"/>
+      <c r="K142" s="11" t="inlineStr"/>
+      <c r="L142" s="11" t="inlineStr"/>
+      <c r="M142" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N142" s="11" t="inlineStr"/>
+      <c r="O142" s="11" t="inlineStr"/>
+      <c r="P142" s="11" t="inlineStr"/>
+      <c r="Q142" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R142" s="11" t="inlineStr"/>
+      <c r="S142" s="11" t="inlineStr"/>
+      <c r="T142" s="11" t="inlineStr"/>
+      <c r="U142" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V142" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W142" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="26" customHeight="1">
+      <c r="A143" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>20260549991</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr"/>
+      <c r="G143" s="11" t="inlineStr"/>
+      <c r="H143" s="11" t="inlineStr"/>
+      <c r="I143" s="11" t="inlineStr"/>
+      <c r="J143" s="11" t="inlineStr"/>
+      <c r="K143" s="11" t="inlineStr"/>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N143" s="11" t="inlineStr"/>
+      <c r="O143" s="11" t="inlineStr"/>
+      <c r="P143" s="11" t="inlineStr"/>
+      <c r="Q143" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R143" s="11" t="inlineStr"/>
+      <c r="S143" s="11" t="inlineStr"/>
+      <c r="T143" s="11" t="inlineStr"/>
+      <c r="U143" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V143" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W143" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="26" customHeight="1">
+      <c r="A144" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>20260550008</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr"/>
+      <c r="G144" s="11" t="inlineStr"/>
+      <c r="H144" s="11" t="inlineStr"/>
+      <c r="I144" s="11" t="inlineStr"/>
+      <c r="J144" s="11" t="inlineStr"/>
+      <c r="K144" s="11" t="inlineStr"/>
+      <c r="L144" s="11" t="inlineStr"/>
+      <c r="M144" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N144" s="11" t="inlineStr"/>
+      <c r="O144" s="11" t="inlineStr"/>
+      <c r="P144" s="11" t="inlineStr"/>
+      <c r="Q144" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R144" s="11" t="inlineStr"/>
+      <c r="S144" s="11" t="inlineStr"/>
+      <c r="T144" s="11" t="inlineStr"/>
+      <c r="U144" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V144" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W144" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="26" customHeight="1">
+      <c r="A145" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>20260550009</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr"/>
+      <c r="G145" s="11" t="inlineStr"/>
+      <c r="H145" s="11" t="inlineStr"/>
+      <c r="I145" s="11" t="inlineStr"/>
+      <c r="J145" s="11" t="inlineStr"/>
+      <c r="K145" s="11" t="inlineStr"/>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N145" s="11" t="inlineStr"/>
+      <c r="O145" s="11" t="inlineStr"/>
+      <c r="P145" s="11" t="inlineStr"/>
+      <c r="Q145" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R145" s="11" t="inlineStr"/>
+      <c r="S145" s="11" t="inlineStr"/>
+      <c r="T145" s="11" t="inlineStr"/>
+      <c r="U145" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V145" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W145" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="26" customHeight="1">
+      <c r="A146" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>20260550010</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr"/>
+      <c r="G146" s="11" t="inlineStr"/>
+      <c r="H146" s="11" t="inlineStr"/>
+      <c r="I146" s="11" t="inlineStr"/>
+      <c r="J146" s="11" t="inlineStr"/>
+      <c r="K146" s="11" t="inlineStr"/>
+      <c r="L146" s="11" t="inlineStr"/>
+      <c r="M146" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N146" s="11" t="inlineStr"/>
+      <c r="O146" s="11" t="inlineStr"/>
+      <c r="P146" s="11" t="inlineStr"/>
+      <c r="Q146" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R146" s="11" t="inlineStr"/>
+      <c r="S146" s="11" t="inlineStr"/>
+      <c r="T146" s="11" t="inlineStr"/>
+      <c r="U146" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V146" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W146" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>20260550080</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr"/>
+      <c r="G147" s="11" t="inlineStr"/>
+      <c r="H147" s="11" t="inlineStr"/>
+      <c r="I147" s="11" t="inlineStr"/>
+      <c r="J147" s="11" t="inlineStr"/>
+      <c r="K147" s="11" t="inlineStr"/>
+      <c r="L147" s="11" t="inlineStr"/>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N147" s="11" t="inlineStr"/>
+      <c r="O147" s="11" t="inlineStr"/>
+      <c r="P147" s="11" t="inlineStr"/>
+      <c r="Q147" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R147" s="11" t="inlineStr"/>
+      <c r="S147" s="11" t="inlineStr"/>
+      <c r="T147" s="11" t="inlineStr"/>
+      <c r="U147" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V147" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W147" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="26" customHeight="1">
+      <c r="A148" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>20260550106</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr"/>
+      <c r="G148" s="11" t="inlineStr"/>
+      <c r="H148" s="11" t="inlineStr"/>
+      <c r="I148" s="11" t="inlineStr"/>
+      <c r="J148" s="11" t="inlineStr"/>
+      <c r="K148" s="11" t="inlineStr"/>
+      <c r="L148" s="11" t="inlineStr"/>
+      <c r="M148" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N148" s="11" t="inlineStr"/>
+      <c r="O148" s="11" t="inlineStr"/>
+      <c r="P148" s="11" t="inlineStr"/>
+      <c r="Q148" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R148" s="11" t="inlineStr"/>
+      <c r="S148" s="11" t="inlineStr"/>
+      <c r="T148" s="11" t="inlineStr"/>
+      <c r="U148" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V148" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W148" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="26" customHeight="1">
+      <c r="A149" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>20260550107</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="inlineStr"/>
+      <c r="G149" s="11" t="inlineStr"/>
+      <c r="H149" s="11" t="inlineStr"/>
+      <c r="I149" s="11" t="inlineStr"/>
+      <c r="J149" s="11" t="inlineStr"/>
+      <c r="K149" s="11" t="inlineStr"/>
+      <c r="L149" s="11" t="inlineStr"/>
+      <c r="M149" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N149" s="11" t="inlineStr"/>
+      <c r="O149" s="11" t="inlineStr"/>
+      <c r="P149" s="11" t="inlineStr"/>
+      <c r="Q149" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R149" s="11" t="inlineStr"/>
+      <c r="S149" s="11" t="inlineStr"/>
+      <c r="T149" s="11" t="inlineStr"/>
+      <c r="U149" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V149" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W149" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="26" customHeight="1">
+      <c r="A150" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C150" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>20260550109</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F150" s="11" t="inlineStr"/>
+      <c r="G150" s="11" t="inlineStr"/>
+      <c r="H150" s="11" t="inlineStr"/>
+      <c r="I150" s="11" t="inlineStr"/>
+      <c r="J150" s="11" t="inlineStr"/>
+      <c r="K150" s="11" t="inlineStr"/>
+      <c r="L150" s="11" t="inlineStr"/>
+      <c r="M150" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N150" s="11" t="inlineStr"/>
+      <c r="O150" s="11" t="inlineStr"/>
+      <c r="P150" s="11" t="inlineStr"/>
+      <c r="Q150" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R150" s="11" t="inlineStr"/>
+      <c r="S150" s="11" t="inlineStr"/>
+      <c r="T150" s="11" t="inlineStr"/>
+      <c r="U150" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V150" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W150" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="26" customHeight="1">
+      <c r="A151" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>20260550111</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="inlineStr"/>
+      <c r="G151" s="11" t="inlineStr"/>
+      <c r="H151" s="11" t="inlineStr"/>
+      <c r="I151" s="11" t="inlineStr"/>
+      <c r="J151" s="11" t="inlineStr"/>
+      <c r="K151" s="11" t="inlineStr"/>
+      <c r="L151" s="11" t="inlineStr"/>
+      <c r="M151" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N151" s="11" t="inlineStr"/>
+      <c r="O151" s="11" t="inlineStr"/>
+      <c r="P151" s="11" t="inlineStr"/>
+      <c r="Q151" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R151" s="11" t="inlineStr"/>
+      <c r="S151" s="11" t="inlineStr"/>
+      <c r="T151" s="11" t="inlineStr"/>
+      <c r="U151" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V151" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W151" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="26" customHeight="1">
+      <c r="A152" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>20260550113</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr"/>
+      <c r="G152" s="11" t="inlineStr"/>
+      <c r="H152" s="11" t="inlineStr"/>
+      <c r="I152" s="11" t="inlineStr"/>
+      <c r="J152" s="11" t="inlineStr"/>
+      <c r="K152" s="11" t="inlineStr"/>
+      <c r="L152" s="11" t="inlineStr"/>
+      <c r="M152" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N152" s="11" t="inlineStr"/>
+      <c r="O152" s="11" t="inlineStr"/>
+      <c r="P152" s="11" t="inlineStr"/>
+      <c r="Q152" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R152" s="11" t="inlineStr"/>
+      <c r="S152" s="11" t="inlineStr"/>
+      <c r="T152" s="11" t="inlineStr"/>
+      <c r="U152" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V152" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W152" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="26" customHeight="1">
+      <c r="A153" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>20260550117</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr"/>
+      <c r="G153" s="11" t="inlineStr"/>
+      <c r="H153" s="11" t="inlineStr"/>
+      <c r="I153" s="11" t="inlineStr"/>
+      <c r="J153" s="11" t="inlineStr"/>
+      <c r="K153" s="11" t="inlineStr"/>
+      <c r="L153" s="11" t="inlineStr"/>
+      <c r="M153" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N153" s="11" t="inlineStr"/>
+      <c r="O153" s="11" t="inlineStr"/>
+      <c r="P153" s="11" t="inlineStr"/>
+      <c r="Q153" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R153" s="11" t="inlineStr"/>
+      <c r="S153" s="11" t="inlineStr"/>
+      <c r="T153" s="11" t="inlineStr"/>
+      <c r="U153" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V153" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W153" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="26" customHeight="1">
+      <c r="A154" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>20260550128</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr"/>
+      <c r="G154" s="11" t="inlineStr"/>
+      <c r="H154" s="11" t="inlineStr"/>
+      <c r="I154" s="11" t="inlineStr"/>
+      <c r="J154" s="11" t="inlineStr"/>
+      <c r="K154" s="11" t="inlineStr"/>
+      <c r="L154" s="11" t="inlineStr"/>
+      <c r="M154" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N154" s="11" t="inlineStr"/>
+      <c r="O154" s="11" t="inlineStr"/>
+      <c r="P154" s="11" t="inlineStr"/>
+      <c r="Q154" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R154" s="11" t="inlineStr"/>
+      <c r="S154" s="11" t="inlineStr"/>
+      <c r="T154" s="11" t="inlineStr"/>
+      <c r="U154" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V154" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W154" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="26" customHeight="1">
+      <c r="A155" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>20260550184</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="inlineStr"/>
+      <c r="G155" s="11" t="inlineStr"/>
+      <c r="H155" s="11" t="inlineStr"/>
+      <c r="I155" s="11" t="inlineStr"/>
+      <c r="J155" s="11" t="inlineStr"/>
+      <c r="K155" s="11" t="inlineStr"/>
+      <c r="L155" s="11" t="inlineStr"/>
+      <c r="M155" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N155" s="11" t="inlineStr"/>
+      <c r="O155" s="11" t="inlineStr"/>
+      <c r="P155" s="11" t="inlineStr"/>
+      <c r="Q155" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R155" s="11" t="inlineStr"/>
+      <c r="S155" s="11" t="inlineStr"/>
+      <c r="T155" s="11" t="inlineStr"/>
+      <c r="U155" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V155" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W155" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="26" customHeight="1">
+      <c r="A156" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>20260550187</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F156" s="11" t="inlineStr"/>
+      <c r="G156" s="11" t="inlineStr"/>
+      <c r="H156" s="11" t="inlineStr"/>
+      <c r="I156" s="11" t="inlineStr"/>
+      <c r="J156" s="11" t="inlineStr"/>
+      <c r="K156" s="11" t="inlineStr"/>
+      <c r="L156" s="11" t="inlineStr"/>
+      <c r="M156" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N156" s="11" t="inlineStr"/>
+      <c r="O156" s="11" t="inlineStr"/>
+      <c r="P156" s="11" t="inlineStr"/>
+      <c r="Q156" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R156" s="11" t="inlineStr"/>
+      <c r="S156" s="11" t="inlineStr"/>
+      <c r="T156" s="11" t="inlineStr"/>
+      <c r="U156" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V156" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W156" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="26" customHeight="1">
+      <c r="A157" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>20260550188</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="inlineStr"/>
+      <c r="G157" s="11" t="inlineStr"/>
+      <c r="H157" s="11" t="inlineStr"/>
+      <c r="I157" s="11" t="inlineStr"/>
+      <c r="J157" s="11" t="inlineStr"/>
+      <c r="K157" s="11" t="inlineStr"/>
+      <c r="L157" s="11" t="inlineStr"/>
+      <c r="M157" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N157" s="11" t="inlineStr"/>
+      <c r="O157" s="11" t="inlineStr"/>
+      <c r="P157" s="11" t="inlineStr"/>
+      <c r="Q157" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R157" s="11" t="inlineStr"/>
+      <c r="S157" s="11" t="inlineStr"/>
+      <c r="T157" s="11" t="inlineStr"/>
+      <c r="U157" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V157" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W157" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="26" customHeight="1">
+      <c r="A158" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>20260550193</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F158" s="11" t="inlineStr"/>
+      <c r="G158" s="11" t="inlineStr"/>
+      <c r="H158" s="11" t="inlineStr"/>
+      <c r="I158" s="11" t="inlineStr"/>
+      <c r="J158" s="11" t="inlineStr"/>
+      <c r="K158" s="11" t="inlineStr"/>
+      <c r="L158" s="11" t="inlineStr"/>
+      <c r="M158" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N158" s="11" t="inlineStr"/>
+      <c r="O158" s="11" t="inlineStr"/>
+      <c r="P158" s="11" t="inlineStr"/>
+      <c r="Q158" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R158" s="11" t="inlineStr"/>
+      <c r="S158" s="11" t="inlineStr"/>
+      <c r="T158" s="11" t="inlineStr"/>
+      <c r="U158" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V158" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W158" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="26" customHeight="1">
+      <c r="A159" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C159" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>20260550203</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F159" s="11" t="inlineStr"/>
+      <c r="G159" s="11" t="inlineStr"/>
+      <c r="H159" s="11" t="inlineStr"/>
+      <c r="I159" s="11" t="inlineStr"/>
+      <c r="J159" s="11" t="inlineStr"/>
+      <c r="K159" s="11" t="inlineStr"/>
+      <c r="L159" s="11" t="inlineStr"/>
+      <c r="M159" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N159" s="11" t="inlineStr"/>
+      <c r="O159" s="11" t="inlineStr"/>
+      <c r="P159" s="11" t="inlineStr"/>
+      <c r="Q159" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R159" s="11" t="inlineStr"/>
+      <c r="S159" s="11" t="inlineStr"/>
+      <c r="T159" s="11" t="inlineStr"/>
+      <c r="U159" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V159" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W159" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="26" customHeight="1">
+      <c r="A160" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D160" s="11" t="inlineStr">
+        <is>
+          <t>20260550226</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F160" s="11" t="inlineStr"/>
+      <c r="G160" s="11" t="inlineStr"/>
+      <c r="H160" s="11" t="inlineStr"/>
+      <c r="I160" s="11" t="inlineStr"/>
+      <c r="J160" s="11" t="inlineStr"/>
+      <c r="K160" s="11" t="inlineStr"/>
+      <c r="L160" s="11" t="inlineStr"/>
+      <c r="M160" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N160" s="11" t="inlineStr"/>
+      <c r="O160" s="11" t="inlineStr"/>
+      <c r="P160" s="11" t="inlineStr"/>
+      <c r="Q160" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R160" s="11" t="inlineStr"/>
+      <c r="S160" s="11" t="inlineStr"/>
+      <c r="T160" s="11" t="inlineStr"/>
+      <c r="U160" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V160" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W160" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="26" customHeight="1">
+      <c r="A161" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C161" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>20260550265</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="inlineStr"/>
+      <c r="G161" s="11" t="inlineStr"/>
+      <c r="H161" s="11" t="inlineStr"/>
+      <c r="I161" s="11" t="inlineStr"/>
+      <c r="J161" s="11" t="inlineStr"/>
+      <c r="K161" s="11" t="inlineStr"/>
+      <c r="L161" s="11" t="inlineStr"/>
+      <c r="M161" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N161" s="11" t="inlineStr"/>
+      <c r="O161" s="11" t="inlineStr"/>
+      <c r="P161" s="11" t="inlineStr"/>
+      <c r="Q161" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R161" s="11" t="inlineStr"/>
+      <c r="S161" s="11" t="inlineStr"/>
+      <c r="T161" s="11" t="inlineStr"/>
+      <c r="U161" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V161" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W161" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="26" customHeight="1">
+      <c r="A162" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="inlineStr">
+        <is>
+          <t>20260550266</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F162" s="11" t="inlineStr"/>
+      <c r="G162" s="11" t="inlineStr"/>
+      <c r="H162" s="11" t="inlineStr"/>
+      <c r="I162" s="11" t="inlineStr"/>
+      <c r="J162" s="11" t="inlineStr"/>
+      <c r="K162" s="11" t="inlineStr"/>
+      <c r="L162" s="11" t="inlineStr"/>
+      <c r="M162" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N162" s="11" t="inlineStr"/>
+      <c r="O162" s="11" t="inlineStr"/>
+      <c r="P162" s="11" t="inlineStr"/>
+      <c r="Q162" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R162" s="11" t="inlineStr"/>
+      <c r="S162" s="11" t="inlineStr"/>
+      <c r="T162" s="11" t="inlineStr"/>
+      <c r="U162" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V162" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W162" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="26" customHeight="1">
+      <c r="A163" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C163" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>20260550267</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="inlineStr"/>
+      <c r="G163" s="11" t="inlineStr"/>
+      <c r="H163" s="11" t="inlineStr"/>
+      <c r="I163" s="11" t="inlineStr"/>
+      <c r="J163" s="11" t="inlineStr"/>
+      <c r="K163" s="11" t="inlineStr"/>
+      <c r="L163" s="11" t="inlineStr"/>
+      <c r="M163" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N163" s="11" t="inlineStr"/>
+      <c r="O163" s="11" t="inlineStr"/>
+      <c r="P163" s="11" t="inlineStr"/>
+      <c r="Q163" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R163" s="11" t="inlineStr"/>
+      <c r="S163" s="11" t="inlineStr"/>
+      <c r="T163" s="11" t="inlineStr"/>
+      <c r="U163" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V163" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W163" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="26" customHeight="1">
+      <c r="A164" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C164" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>20260550268</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F164" s="11" t="inlineStr"/>
+      <c r="G164" s="11" t="inlineStr"/>
+      <c r="H164" s="11" t="inlineStr"/>
+      <c r="I164" s="11" t="inlineStr"/>
+      <c r="J164" s="11" t="inlineStr"/>
+      <c r="K164" s="11" t="inlineStr"/>
+      <c r="L164" s="11" t="inlineStr"/>
+      <c r="M164" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N164" s="11" t="inlineStr"/>
+      <c r="O164" s="11" t="inlineStr"/>
+      <c r="P164" s="11" t="inlineStr"/>
+      <c r="Q164" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R164" s="11" t="inlineStr"/>
+      <c r="S164" s="11" t="inlineStr"/>
+      <c r="T164" s="11" t="inlineStr"/>
+      <c r="U164" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V164" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W164" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="26" customHeight="1">
+      <c r="A165" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C165" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>20260550269</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F165" s="11" t="inlineStr"/>
+      <c r="G165" s="11" t="inlineStr"/>
+      <c r="H165" s="11" t="inlineStr"/>
+      <c r="I165" s="11" t="inlineStr"/>
+      <c r="J165" s="11" t="inlineStr"/>
+      <c r="K165" s="11" t="inlineStr"/>
+      <c r="L165" s="11" t="inlineStr"/>
+      <c r="M165" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N165" s="11" t="inlineStr"/>
+      <c r="O165" s="11" t="inlineStr"/>
+      <c r="P165" s="11" t="inlineStr"/>
+      <c r="Q165" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R165" s="11" t="inlineStr"/>
+      <c r="S165" s="11" t="inlineStr"/>
+      <c r="T165" s="11" t="inlineStr"/>
+      <c r="U165" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V165" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W165" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="26" customHeight="1">
+      <c r="A166" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C166" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="inlineStr">
+        <is>
+          <t>20260550270</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr"/>
+      <c r="G166" s="11" t="inlineStr"/>
+      <c r="H166" s="11" t="inlineStr"/>
+      <c r="I166" s="11" t="inlineStr"/>
+      <c r="J166" s="11" t="inlineStr"/>
+      <c r="K166" s="11" t="inlineStr"/>
+      <c r="L166" s="11" t="inlineStr"/>
+      <c r="M166" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N166" s="11" t="inlineStr"/>
+      <c r="O166" s="11" t="inlineStr"/>
+      <c r="P166" s="11" t="inlineStr"/>
+      <c r="Q166" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R166" s="11" t="inlineStr"/>
+      <c r="S166" s="11" t="inlineStr"/>
+      <c r="T166" s="11" t="inlineStr"/>
+      <c r="U166" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V166" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W166" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="26" customHeight="1">
+      <c r="A167" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C167" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>20260550337</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="inlineStr"/>
+      <c r="G167" s="11" t="inlineStr"/>
+      <c r="H167" s="11" t="inlineStr"/>
+      <c r="I167" s="11" t="inlineStr"/>
+      <c r="J167" s="11" t="inlineStr"/>
+      <c r="K167" s="11" t="inlineStr"/>
+      <c r="L167" s="11" t="inlineStr"/>
+      <c r="M167" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N167" s="11" t="inlineStr"/>
+      <c r="O167" s="11" t="inlineStr"/>
+      <c r="P167" s="11" t="inlineStr"/>
+      <c r="Q167" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R167" s="11" t="inlineStr"/>
+      <c r="S167" s="11" t="inlineStr"/>
+      <c r="T167" s="11" t="inlineStr"/>
+      <c r="U167" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V167" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W167" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W118"/>
+  <autoFilter ref="A1:W167"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
@@ -8790,6 +11881,55 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W116" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W117" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W167" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8818,7 +11958,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-09-18 05:34</t>
+          <t>Run: 2026-09-19 05:32</t>
         </is>
       </c>
     </row>
@@ -8833,7 +11973,7 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>117</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5">
@@ -8843,7 +11983,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -8863,7 +12003,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8">
@@ -8873,7 +12013,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -8883,7 +12023,7 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -8905,17 +12045,17 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>79</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Notice of Trustee Sale</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="B13" s="14" t="n">
@@ -8925,31 +12065,31 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-09-20 05:40</t>
+          <t>Run: 2026-09-21 05:50</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,28 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00374151"/>
       <sz val="10"/>
     </font>
     <font>
@@ -49,7 +71,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +81,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2433"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,14 +120,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -606,8 +656,1754 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>20260563011</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2801 N. Litchfield Rd., #75</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Goodyear</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>85395</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>20260562756</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr"/>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>20260561372</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr"/>
+      <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr"/>
+      <c r="S4" s="6" t="inlineStr"/>
+      <c r="T4" s="6" t="inlineStr"/>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>20260561373</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr"/>
+      <c r="S5" s="6" t="inlineStr"/>
+      <c r="T5" s="6" t="inlineStr"/>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>20260561378</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="6" t="inlineStr"/>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>20260562199</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="6" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>20260562308</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="6" t="inlineStr"/>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>20260562328</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>20260562363</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="6" t="inlineStr"/>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>20260562364</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="6" t="inlineStr"/>
+      <c r="T11" s="6" t="inlineStr"/>
+      <c r="U11" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V11" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>20260562428</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr"/>
+      <c r="S12" s="6" t="inlineStr"/>
+      <c r="T12" s="6" t="inlineStr"/>
+      <c r="U12" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>20260562445</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="6" t="inlineStr"/>
+      <c r="T13" s="6" t="inlineStr"/>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>20260562536</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="6" t="inlineStr"/>
+      <c r="T14" s="6" t="inlineStr"/>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>20260562810</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Superior Court |</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="6" t="inlineStr"/>
+      <c r="T15" s="6" t="inlineStr"/>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>20260563165</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="6" t="inlineStr"/>
+      <c r="T16" s="6" t="inlineStr"/>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>20260563293</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Superior Court in case no. CV2024-015783 on February 24</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="6" t="inlineStr"/>
+      <c r="T17" s="6" t="inlineStr"/>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>20260563301</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="6" t="inlineStr"/>
+      <c r="T18" s="6" t="inlineStr"/>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>20260563302</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr"/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="6" t="inlineStr"/>
+      <c r="T19" s="6" t="inlineStr"/>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>20260563510</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr"/>
+      <c r="O20" s="6" t="inlineStr"/>
+      <c r="P20" s="6" t="inlineStr"/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr"/>
+      <c r="S20" s="6" t="inlineStr"/>
+      <c r="T20" s="6" t="inlineStr"/>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>20260562677</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr"/>
+      <c r="P21" s="6" t="inlineStr"/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr"/>
+      <c r="S21" s="6" t="inlineStr"/>
+      <c r="T21" s="6" t="inlineStr"/>
+      <c r="U21" s="6" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>20260562679</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA |</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr"/>
+      <c r="U22" s="6" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>20260562681</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr"/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr"/>
+      <c r="S23" s="6" t="inlineStr"/>
+      <c r="T23" s="6" t="inlineStr"/>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>20260562683</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr"/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr"/>
+      <c r="S24" s="6" t="inlineStr"/>
+      <c r="T24" s="6" t="inlineStr"/>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>20260562685</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr"/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr"/>
+      <c r="S25" s="6" t="inlineStr"/>
+      <c r="T25" s="6" t="inlineStr"/>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>20260562688</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr"/>
+      <c r="P26" s="6" t="inlineStr"/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr"/>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>102-23-015</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr"/>
+      <c r="U26" s="6" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>20260563023</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W27"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -618,7 +2414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -626,7 +2422,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -635,88 +2431,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-09-25 05:52</t>
+          <t>Run: 2026-09-26 05:54</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="A3" s="9" t="inlineStr"/>
+      <c r="B3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>With Property Address</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>With Mailing Address</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>With Property Address</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>PDF Parsed</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Score 70+ (Hot)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>With Mailing Address</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>PDF Parsed</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Score 70+ (Hot)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Score 50-69 (Warm)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
+      <c r="B9" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" s="9" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>By Category</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-09-27 06:16</t>
+          <t>Run: 2026-09-28 06:27</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +34,33 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00374151"/>
       <sz val="10"/>
     </font>
     <font>
@@ -49,7 +78,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +88,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2433"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,14 +127,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -606,8 +666,8196 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>20260564080</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
+        <v>124086.41</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>501-74-893</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>20260565570</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>25625 North Singbush Loop</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>85083</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>201-33-41722</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>20260564110</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr"/>
+      <c r="P4" s="7" t="inlineStr"/>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr"/>
+      <c r="S4" s="7" t="inlineStr"/>
+      <c r="T4" s="7" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Lis pendens; New this week</t>
+        </is>
+      </c>
+      <c r="V4" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>20260564628</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>2000-11-06</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr"/>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr"/>
+      <c r="S5" s="7" t="inlineStr"/>
+      <c r="T5" s="7" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Lis pendens; New this week</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>20260564771</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr"/>
+      <c r="P6" s="7" t="inlineStr"/>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr"/>
+      <c r="S6" s="7" t="inlineStr"/>
+      <c r="T6" s="7" t="inlineStr"/>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Lis pendens; New this week</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>20260564896</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>2000-11-06</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr"/>
+      <c r="S7" s="7" t="inlineStr"/>
+      <c r="T7" s="7" t="inlineStr"/>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Lis pendens; New this week</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>20260564962</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr"/>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr"/>
+      <c r="S8" s="7" t="inlineStr"/>
+      <c r="T8" s="7" t="inlineStr"/>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>Lis pendens; New this week</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>20260563722</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr"/>
+      <c r="S9" s="7" t="inlineStr"/>
+      <c r="T9" s="7" t="inlineStr"/>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>20260563723</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr"/>
+      <c r="P10" s="7" t="inlineStr"/>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr"/>
+      <c r="S10" s="7" t="inlineStr"/>
+      <c r="T10" s="7" t="inlineStr"/>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>20260563879</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr"/>
+      <c r="S11" s="7" t="inlineStr"/>
+      <c r="T11" s="7" t="inlineStr"/>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>20260564166</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr"/>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr"/>
+      <c r="S12" s="7" t="inlineStr"/>
+      <c r="T12" s="7" t="inlineStr"/>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>20260564315</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr"/>
+      <c r="T13" s="7" t="inlineStr"/>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>20260564454</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>201 W JEFFERSON ST</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr"/>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr"/>
+      <c r="S14" s="7" t="inlineStr"/>
+      <c r="T14" s="7" t="inlineStr"/>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>20260564769</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr"/>
+      <c r="T15" s="7" t="inlineStr"/>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>20260564897</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr"/>
+      <c r="T16" s="7" t="inlineStr"/>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>20260565292</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr"/>
+      <c r="O17" s="7" t="inlineStr"/>
+      <c r="P17" s="7" t="inlineStr"/>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr"/>
+      <c r="S17" s="7" t="inlineStr"/>
+      <c r="T17" s="7" t="inlineStr"/>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>20260565293</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr"/>
+      <c r="T18" s="7" t="inlineStr"/>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>20260565338</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr"/>
+      <c r="O19" s="7" t="inlineStr"/>
+      <c r="P19" s="7" t="inlineStr"/>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr"/>
+      <c r="S19" s="7" t="inlineStr"/>
+      <c r="T19" s="7" t="inlineStr"/>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>20260565477</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court in case no. CV2025-021683 on September 23</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr"/>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr"/>
+      <c r="S20" s="7" t="inlineStr"/>
+      <c r="T20" s="7" t="inlineStr"/>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>20260565754</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr"/>
+      <c r="T21" s="7" t="inlineStr"/>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>20260565774</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr"/>
+      <c r="T22" s="7" t="inlineStr"/>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>20260565838</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>145-10-084</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr"/>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>20260565860</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr"/>
+      <c r="S24" s="7" t="inlineStr"/>
+      <c r="T24" s="7" t="inlineStr"/>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>20260565935</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr"/>
+      <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>20260565936</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr"/>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr"/>
+      <c r="S26" s="7" t="inlineStr"/>
+      <c r="T26" s="7" t="inlineStr"/>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>20260565938</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr"/>
+      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr"/>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr"/>
+      <c r="S27" s="7" t="inlineStr"/>
+      <c r="T27" s="7" t="inlineStr"/>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>20260565939</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr"/>
+      <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr"/>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr"/>
+      <c r="S28" s="7" t="inlineStr"/>
+      <c r="T28" s="7" t="inlineStr"/>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>20260565940</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr"/>
+      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr"/>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr"/>
+      <c r="S29" s="7" t="inlineStr"/>
+      <c r="T29" s="7" t="inlineStr"/>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>20260565941</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr"/>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr"/>
+      <c r="S30" s="7" t="inlineStr"/>
+      <c r="T30" s="7" t="inlineStr"/>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V30" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>20260565942</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr"/>
+      <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr"/>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R31" s="7" t="inlineStr"/>
+      <c r="S31" s="7" t="inlineStr"/>
+      <c r="T31" s="7" t="inlineStr"/>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>20260565943</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr"/>
+      <c r="O32" s="7" t="inlineStr"/>
+      <c r="P32" s="7" t="inlineStr"/>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr"/>
+      <c r="S32" s="7" t="inlineStr"/>
+      <c r="T32" s="7" t="inlineStr"/>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V32" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>20260565944</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr"/>
+      <c r="O33" s="7" t="inlineStr"/>
+      <c r="P33" s="7" t="inlineStr"/>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R33" s="7" t="inlineStr"/>
+      <c r="S33" s="7" t="inlineStr"/>
+      <c r="T33" s="7" t="inlineStr"/>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V33" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>20260565945</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr"/>
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr"/>
+      <c r="O34" s="7" t="inlineStr"/>
+      <c r="P34" s="7" t="inlineStr"/>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R34" s="7" t="inlineStr"/>
+      <c r="S34" s="7" t="inlineStr"/>
+      <c r="T34" s="7" t="inlineStr"/>
+      <c r="U34" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V34" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>20260565946</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr"/>
+      <c r="O35" s="7" t="inlineStr"/>
+      <c r="P35" s="7" t="inlineStr"/>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R35" s="7" t="inlineStr"/>
+      <c r="S35" s="7" t="inlineStr"/>
+      <c r="T35" s="7" t="inlineStr"/>
+      <c r="U35" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V35" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>20260565947</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr"/>
+      <c r="O36" s="7" t="inlineStr"/>
+      <c r="P36" s="7" t="inlineStr"/>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R36" s="7" t="inlineStr"/>
+      <c r="S36" s="7" t="inlineStr"/>
+      <c r="T36" s="7" t="inlineStr"/>
+      <c r="U36" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V36" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>20260565948</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr"/>
+      <c r="O37" s="7" t="inlineStr"/>
+      <c r="P37" s="7" t="inlineStr"/>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R37" s="7" t="inlineStr"/>
+      <c r="S37" s="7" t="inlineStr"/>
+      <c r="T37" s="7" t="inlineStr"/>
+      <c r="U37" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V37" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>20260565949</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr"/>
+      <c r="O38" s="7" t="inlineStr"/>
+      <c r="P38" s="7" t="inlineStr"/>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R38" s="7" t="inlineStr"/>
+      <c r="S38" s="7" t="inlineStr"/>
+      <c r="T38" s="7" t="inlineStr"/>
+      <c r="U38" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V38" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W38" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>20260565950</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr"/>
+      <c r="O39" s="7" t="inlineStr"/>
+      <c r="P39" s="7" t="inlineStr"/>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R39" s="7" t="inlineStr"/>
+      <c r="S39" s="7" t="inlineStr"/>
+      <c r="T39" s="7" t="inlineStr"/>
+      <c r="U39" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V39" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W39" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>20260565951</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr"/>
+      <c r="O40" s="7" t="inlineStr"/>
+      <c r="P40" s="7" t="inlineStr"/>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R40" s="7" t="inlineStr"/>
+      <c r="S40" s="7" t="inlineStr"/>
+      <c r="T40" s="7" t="inlineStr"/>
+      <c r="U40" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V40" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W40" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>20260565952</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr"/>
+      <c r="O41" s="7" t="inlineStr"/>
+      <c r="P41" s="7" t="inlineStr"/>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R41" s="7" t="inlineStr"/>
+      <c r="S41" s="7" t="inlineStr"/>
+      <c r="T41" s="7" t="inlineStr"/>
+      <c r="U41" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V41" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W41" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>20260565953</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr"/>
+      <c r="O42" s="7" t="inlineStr"/>
+      <c r="P42" s="7" t="inlineStr"/>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R42" s="7" t="inlineStr"/>
+      <c r="S42" s="7" t="inlineStr"/>
+      <c r="T42" s="7" t="inlineStr"/>
+      <c r="U42" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V42" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>20260566013</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr"/>
+      <c r="O43" s="7" t="inlineStr"/>
+      <c r="P43" s="7" t="inlineStr"/>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R43" s="7" t="inlineStr"/>
+      <c r="S43" s="7" t="inlineStr"/>
+      <c r="T43" s="7" t="inlineStr"/>
+      <c r="U43" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V43" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W43" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>20260566046</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr"/>
+      <c r="H44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr"/>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr"/>
+      <c r="O44" s="7" t="inlineStr"/>
+      <c r="P44" s="7" t="inlineStr"/>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R44" s="7" t="inlineStr"/>
+      <c r="S44" s="7" t="inlineStr"/>
+      <c r="T44" s="7" t="inlineStr"/>
+      <c r="U44" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V44" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>20260566245</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr"/>
+      <c r="O45" s="7" t="inlineStr"/>
+      <c r="P45" s="7" t="inlineStr"/>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R45" s="7" t="inlineStr"/>
+      <c r="S45" s="7" t="inlineStr"/>
+      <c r="T45" s="7" t="inlineStr"/>
+      <c r="U45" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V45" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W45" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>20260566107</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr"/>
+      <c r="O46" s="7" t="inlineStr"/>
+      <c r="P46" s="7" t="inlineStr"/>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R46" s="7" t="inlineStr"/>
+      <c r="S46" s="7" t="inlineStr"/>
+      <c r="T46" s="7" t="inlineStr"/>
+      <c r="U46" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V46" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>20260564398</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr"/>
+      <c r="L47" s="7" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr"/>
+      <c r="O47" s="7" t="inlineStr"/>
+      <c r="P47" s="7" t="inlineStr"/>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R47" s="7" t="inlineStr"/>
+      <c r="S47" s="7" t="inlineStr"/>
+      <c r="T47" s="7" t="inlineStr"/>
+      <c r="U47" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V47" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W47" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>20260564623</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr"/>
+      <c r="O48" s="7" t="inlineStr"/>
+      <c r="P48" s="7" t="inlineStr"/>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R48" s="7" t="inlineStr"/>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>501-78-039</t>
+        </is>
+      </c>
+      <c r="T48" s="7" t="inlineStr"/>
+      <c r="U48" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V48" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W48" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>20260564633</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court of Arizona/ Maricopa County</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr"/>
+      <c r="O49" s="7" t="inlineStr"/>
+      <c r="P49" s="7" t="inlineStr"/>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R49" s="7" t="inlineStr"/>
+      <c r="S49" s="7" t="inlineStr"/>
+      <c r="T49" s="7" t="inlineStr"/>
+      <c r="U49" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V49" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W49" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>20260564918</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr"/>
+      <c r="O50" s="7" t="inlineStr"/>
+      <c r="P50" s="7" t="inlineStr"/>
+      <c r="Q50" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R50" s="7" t="inlineStr"/>
+      <c r="S50" s="7" t="inlineStr"/>
+      <c r="T50" s="7" t="inlineStr"/>
+      <c r="U50" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V50" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>20260564997</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr"/>
+      <c r="O51" s="7" t="inlineStr"/>
+      <c r="P51" s="7" t="inlineStr"/>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R51" s="7" t="inlineStr"/>
+      <c r="S51" s="7" t="inlineStr"/>
+      <c r="T51" s="7" t="inlineStr"/>
+      <c r="U51" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V51" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W51" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>20260565160</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr"/>
+      <c r="O52" s="7" t="inlineStr"/>
+      <c r="P52" s="7" t="inlineStr"/>
+      <c r="Q52" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R52" s="7" t="inlineStr"/>
+      <c r="S52" s="7" t="inlineStr"/>
+      <c r="T52" s="7" t="inlineStr"/>
+      <c r="U52" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V52" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W52" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>20260565215</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr"/>
+      <c r="O53" s="7" t="inlineStr"/>
+      <c r="P53" s="7" t="inlineStr"/>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R53" s="7" t="inlineStr"/>
+      <c r="S53" s="7" t="inlineStr"/>
+      <c r="T53" s="7" t="inlineStr"/>
+      <c r="U53" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V53" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>20260565283</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court of Arizona</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr"/>
+      <c r="O54" s="7" t="inlineStr"/>
+      <c r="P54" s="7" t="inlineStr"/>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R54" s="7" t="inlineStr"/>
+      <c r="S54" s="7" t="inlineStr"/>
+      <c r="T54" s="7" t="inlineStr"/>
+      <c r="U54" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V54" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W54" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>20260565372</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr"/>
+      <c r="O55" s="7" t="inlineStr"/>
+      <c r="P55" s="7" t="inlineStr"/>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R55" s="7" t="inlineStr"/>
+      <c r="S55" s="7" t="inlineStr"/>
+      <c r="T55" s="7" t="inlineStr"/>
+      <c r="U55" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V55" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W55" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>20260565524</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT .</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr"/>
+      <c r="L56" s="7" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr"/>
+      <c r="O56" s="7" t="inlineStr"/>
+      <c r="P56" s="7" t="inlineStr"/>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R56" s="7" t="inlineStr"/>
+      <c r="S56" s="7" t="inlineStr"/>
+      <c r="T56" s="7" t="inlineStr"/>
+      <c r="U56" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V56" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W56" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>20260565728</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr"/>
+      <c r="O57" s="7" t="inlineStr"/>
+      <c r="P57" s="7" t="inlineStr"/>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R57" s="7" t="inlineStr"/>
+      <c r="S57" s="7" t="inlineStr"/>
+      <c r="T57" s="7" t="inlineStr"/>
+      <c r="U57" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V57" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W57" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>20260566028</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr"/>
+      <c r="L58" s="7" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr"/>
+      <c r="O58" s="7" t="inlineStr"/>
+      <c r="P58" s="7" t="inlineStr"/>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R58" s="7" t="inlineStr"/>
+      <c r="S58" s="7" t="inlineStr"/>
+      <c r="T58" s="7" t="inlineStr"/>
+      <c r="U58" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V58" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W58" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>20260563817</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr"/>
+      <c r="K59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr"/>
+      <c r="O59" s="7" t="inlineStr"/>
+      <c r="P59" s="7" t="inlineStr"/>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R59" s="7" t="inlineStr"/>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>217-02-688</t>
+        </is>
+      </c>
+      <c r="T59" s="7" t="inlineStr"/>
+      <c r="U59" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V59" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W59" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>20260564078</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr"/>
+      <c r="J60" s="7" t="inlineStr"/>
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr"/>
+      <c r="O60" s="7" t="inlineStr"/>
+      <c r="P60" s="7" t="inlineStr"/>
+      <c r="Q60" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R60" s="7" t="inlineStr"/>
+      <c r="S60" s="7" t="inlineStr"/>
+      <c r="T60" s="7" t="inlineStr"/>
+      <c r="U60" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V60" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W60" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>20260564360</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="7" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr"/>
+      <c r="K61" s="7" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr"/>
+      <c r="O61" s="7" t="inlineStr"/>
+      <c r="P61" s="7" t="inlineStr"/>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R61" s="7" t="inlineStr"/>
+      <c r="S61" s="7" t="inlineStr"/>
+      <c r="T61" s="7" t="inlineStr"/>
+      <c r="U61" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V61" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W61" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>20260564508</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr"/>
+      <c r="H62" s="7" t="inlineStr"/>
+      <c r="I62" s="7" t="inlineStr"/>
+      <c r="J62" s="7" t="inlineStr"/>
+      <c r="K62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr"/>
+      <c r="O62" s="7" t="inlineStr"/>
+      <c r="P62" s="7" t="inlineStr"/>
+      <c r="Q62" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R62" s="7" t="inlineStr"/>
+      <c r="S62" s="7" t="inlineStr"/>
+      <c r="T62" s="7" t="inlineStr"/>
+      <c r="U62" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V62" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W62" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>20260564803</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr"/>
+      <c r="K63" s="7" t="inlineStr"/>
+      <c r="L63" s="7" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr"/>
+      <c r="O63" s="7" t="inlineStr"/>
+      <c r="P63" s="7" t="inlineStr"/>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R63" s="7" t="inlineStr"/>
+      <c r="S63" s="7" t="inlineStr"/>
+      <c r="T63" s="7" t="inlineStr"/>
+      <c r="U63" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V63" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W63" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>20260565042</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr"/>
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr"/>
+      <c r="O64" s="7" t="inlineStr"/>
+      <c r="P64" s="7" t="inlineStr"/>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R64" s="7" t="inlineStr"/>
+      <c r="S64" s="7" t="inlineStr"/>
+      <c r="T64" s="7" t="inlineStr"/>
+      <c r="U64" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V64" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W64" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>20260565085</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+      <c r="K65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr"/>
+      <c r="O65" s="7" t="inlineStr"/>
+      <c r="P65" s="7" t="inlineStr"/>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R65" s="7" t="inlineStr"/>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>300-02-944</t>
+        </is>
+      </c>
+      <c r="T65" s="7" t="inlineStr"/>
+      <c r="U65" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V65" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W65" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>20260565349</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="7" t="inlineStr"/>
+      <c r="I66" s="7" t="inlineStr"/>
+      <c r="J66" s="7" t="inlineStr"/>
+      <c r="K66" s="7" t="inlineStr"/>
+      <c r="L66" s="7" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr"/>
+      <c r="O66" s="7" t="inlineStr"/>
+      <c r="P66" s="7" t="inlineStr"/>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R66" s="7" t="inlineStr"/>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>304-68-155202</t>
+        </is>
+      </c>
+      <c r="T66" s="7" t="inlineStr"/>
+      <c r="U66" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V66" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W66" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>20260565379</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr"/>
+      <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr"/>
+      <c r="O67" s="7" t="inlineStr"/>
+      <c r="P67" s="7" t="inlineStr"/>
+      <c r="Q67" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R67" s="7" t="inlineStr"/>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>176-21-172</t>
+        </is>
+      </c>
+      <c r="T67" s="7" t="inlineStr"/>
+      <c r="U67" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V67" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W67" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>20260565987</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr"/>
+      <c r="G68" s="7" t="inlineStr"/>
+      <c r="H68" s="7" t="inlineStr"/>
+      <c r="I68" s="7" t="inlineStr"/>
+      <c r="J68" s="7" t="inlineStr"/>
+      <c r="K68" s="7" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr"/>
+      <c r="O68" s="7" t="inlineStr"/>
+      <c r="P68" s="7" t="inlineStr"/>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R68" s="7" t="inlineStr"/>
+      <c r="S68" s="7" t="inlineStr"/>
+      <c r="T68" s="7" t="inlineStr"/>
+      <c r="U68" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V68" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W68" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>20260563727</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr"/>
+      <c r="J69" s="7" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr"/>
+      <c r="O69" s="7" t="inlineStr"/>
+      <c r="P69" s="7" t="inlineStr"/>
+      <c r="Q69" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R69" s="7" t="inlineStr"/>
+      <c r="S69" s="7" t="inlineStr"/>
+      <c r="T69" s="7" t="inlineStr"/>
+      <c r="U69" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V69" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W69" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>20260563728</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr"/>
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr"/>
+      <c r="J70" s="7" t="inlineStr"/>
+      <c r="K70" s="7" t="inlineStr"/>
+      <c r="L70" s="7" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr"/>
+      <c r="O70" s="7" t="inlineStr"/>
+      <c r="P70" s="7" t="inlineStr"/>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R70" s="7" t="inlineStr"/>
+      <c r="S70" s="7" t="inlineStr"/>
+      <c r="T70" s="7" t="inlineStr"/>
+      <c r="U70" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V70" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W70" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>20260563729</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="7" t="inlineStr"/>
+      <c r="I71" s="7" t="inlineStr"/>
+      <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr"/>
+      <c r="O71" s="7" t="inlineStr"/>
+      <c r="P71" s="7" t="inlineStr"/>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R71" s="7" t="inlineStr"/>
+      <c r="S71" s="7" t="inlineStr"/>
+      <c r="T71" s="7" t="inlineStr"/>
+      <c r="U71" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V71" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W71" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>20260563730</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr"/>
+      <c r="J72" s="7" t="inlineStr"/>
+      <c r="K72" s="7" t="inlineStr"/>
+      <c r="L72" s="7" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr"/>
+      <c r="O72" s="7" t="inlineStr"/>
+      <c r="P72" s="7" t="inlineStr"/>
+      <c r="Q72" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R72" s="7" t="inlineStr"/>
+      <c r="S72" s="7" t="inlineStr"/>
+      <c r="T72" s="7" t="inlineStr"/>
+      <c r="U72" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V72" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W72" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>20260563731</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+      <c r="K73" s="7" t="inlineStr"/>
+      <c r="L73" s="7" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N73" s="7" t="inlineStr"/>
+      <c r="O73" s="7" t="inlineStr"/>
+      <c r="P73" s="7" t="inlineStr"/>
+      <c r="Q73" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R73" s="7" t="inlineStr"/>
+      <c r="S73" s="7" t="inlineStr"/>
+      <c r="T73" s="7" t="inlineStr"/>
+      <c r="U73" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V73" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W73" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>20260563732</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr"/>
+      <c r="J74" s="7" t="inlineStr"/>
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr"/>
+      <c r="O74" s="7" t="inlineStr"/>
+      <c r="P74" s="7" t="inlineStr"/>
+      <c r="Q74" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R74" s="7" t="inlineStr"/>
+      <c r="S74" s="7" t="inlineStr"/>
+      <c r="T74" s="7" t="inlineStr"/>
+      <c r="U74" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V74" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W74" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>20260563733</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr"/>
+      <c r="O75" s="7" t="inlineStr"/>
+      <c r="P75" s="7" t="inlineStr"/>
+      <c r="Q75" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R75" s="7" t="inlineStr"/>
+      <c r="S75" s="7" t="inlineStr"/>
+      <c r="T75" s="7" t="inlineStr"/>
+      <c r="U75" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V75" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W75" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>20260563734</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr"/>
+      <c r="H76" s="7" t="inlineStr"/>
+      <c r="I76" s="7" t="inlineStr"/>
+      <c r="J76" s="7" t="inlineStr"/>
+      <c r="K76" s="7" t="inlineStr"/>
+      <c r="L76" s="7" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N76" s="7" t="inlineStr"/>
+      <c r="O76" s="7" t="inlineStr"/>
+      <c r="P76" s="7" t="inlineStr"/>
+      <c r="Q76" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R76" s="7" t="inlineStr"/>
+      <c r="S76" s="7" t="inlineStr"/>
+      <c r="T76" s="7" t="inlineStr"/>
+      <c r="U76" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V76" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W76" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>20260563735</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+      <c r="K77" s="7" t="inlineStr"/>
+      <c r="L77" s="7" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr"/>
+      <c r="O77" s="7" t="inlineStr"/>
+      <c r="P77" s="7" t="inlineStr"/>
+      <c r="Q77" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R77" s="7" t="inlineStr"/>
+      <c r="S77" s="7" t="inlineStr"/>
+      <c r="T77" s="7" t="inlineStr"/>
+      <c r="U77" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V77" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W77" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>20260563736</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr"/>
+      <c r="K78" s="7" t="inlineStr"/>
+      <c r="L78" s="7" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N78" s="7" t="inlineStr"/>
+      <c r="O78" s="7" t="inlineStr"/>
+      <c r="P78" s="7" t="inlineStr"/>
+      <c r="Q78" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R78" s="7" t="inlineStr"/>
+      <c r="S78" s="7" t="inlineStr"/>
+      <c r="T78" s="7" t="inlineStr"/>
+      <c r="U78" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V78" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W78" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>20260563737</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr"/>
+      <c r="K79" s="7" t="inlineStr"/>
+      <c r="L79" s="7" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr"/>
+      <c r="O79" s="7" t="inlineStr"/>
+      <c r="P79" s="7" t="inlineStr"/>
+      <c r="Q79" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R79" s="7" t="inlineStr"/>
+      <c r="S79" s="7" t="inlineStr"/>
+      <c r="T79" s="7" t="inlineStr"/>
+      <c r="U79" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V79" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W79" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="26" customHeight="1">
+      <c r="A80" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>20260563738</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr"/>
+      <c r="G80" s="7" t="inlineStr"/>
+      <c r="H80" s="7" t="inlineStr"/>
+      <c r="I80" s="7" t="inlineStr"/>
+      <c r="J80" s="7" t="inlineStr"/>
+      <c r="K80" s="7" t="inlineStr"/>
+      <c r="L80" s="7" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N80" s="7" t="inlineStr"/>
+      <c r="O80" s="7" t="inlineStr"/>
+      <c r="P80" s="7" t="inlineStr"/>
+      <c r="Q80" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R80" s="7" t="inlineStr"/>
+      <c r="S80" s="7" t="inlineStr"/>
+      <c r="T80" s="7" t="inlineStr"/>
+      <c r="U80" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V80" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W80" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>20260563739</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
+      <c r="L81" s="7" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr"/>
+      <c r="O81" s="7" t="inlineStr"/>
+      <c r="P81" s="7" t="inlineStr"/>
+      <c r="Q81" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R81" s="7" t="inlineStr"/>
+      <c r="S81" s="7" t="inlineStr"/>
+      <c r="T81" s="7" t="inlineStr"/>
+      <c r="U81" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V81" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W81" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="26" customHeight="1">
+      <c r="A82" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>20260563740</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr"/>
+      <c r="I82" s="7" t="inlineStr"/>
+      <c r="J82" s="7" t="inlineStr"/>
+      <c r="K82" s="7" t="inlineStr"/>
+      <c r="L82" s="7" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N82" s="7" t="inlineStr"/>
+      <c r="O82" s="7" t="inlineStr"/>
+      <c r="P82" s="7" t="inlineStr"/>
+      <c r="Q82" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R82" s="7" t="inlineStr"/>
+      <c r="S82" s="7" t="inlineStr"/>
+      <c r="T82" s="7" t="inlineStr"/>
+      <c r="U82" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V82" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W82" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>20260563741</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr"/>
+      <c r="J83" s="7" t="inlineStr"/>
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N83" s="7" t="inlineStr"/>
+      <c r="O83" s="7" t="inlineStr"/>
+      <c r="P83" s="7" t="inlineStr"/>
+      <c r="Q83" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R83" s="7" t="inlineStr"/>
+      <c r="S83" s="7" t="inlineStr"/>
+      <c r="T83" s="7" t="inlineStr"/>
+      <c r="U83" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V83" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W83" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>20260563742</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr"/>
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="7" t="inlineStr"/>
+      <c r="K84" s="7" t="inlineStr"/>
+      <c r="L84" s="7" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N84" s="7" t="inlineStr"/>
+      <c r="O84" s="7" t="inlineStr"/>
+      <c r="P84" s="7" t="inlineStr"/>
+      <c r="Q84" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R84" s="7" t="inlineStr"/>
+      <c r="S84" s="7" t="inlineStr"/>
+      <c r="T84" s="7" t="inlineStr"/>
+      <c r="U84" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V84" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W84" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>20260563743</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr"/>
+      <c r="J85" s="7" t="inlineStr"/>
+      <c r="K85" s="7" t="inlineStr"/>
+      <c r="L85" s="7" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N85" s="7" t="inlineStr"/>
+      <c r="O85" s="7" t="inlineStr"/>
+      <c r="P85" s="7" t="inlineStr"/>
+      <c r="Q85" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R85" s="7" t="inlineStr"/>
+      <c r="S85" s="7" t="inlineStr"/>
+      <c r="T85" s="7" t="inlineStr"/>
+      <c r="U85" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V85" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W85" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>20260563744</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr"/>
+      <c r="K86" s="7" t="inlineStr"/>
+      <c r="L86" s="7" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr"/>
+      <c r="O86" s="7" t="inlineStr"/>
+      <c r="P86" s="7" t="inlineStr"/>
+      <c r="Q86" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R86" s="7" t="inlineStr"/>
+      <c r="S86" s="7" t="inlineStr"/>
+      <c r="T86" s="7" t="inlineStr"/>
+      <c r="U86" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V86" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W86" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>20260563745</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr"/>
+      <c r="L87" s="7" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr"/>
+      <c r="O87" s="7" t="inlineStr"/>
+      <c r="P87" s="7" t="inlineStr"/>
+      <c r="Q87" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R87" s="7" t="inlineStr"/>
+      <c r="S87" s="7" t="inlineStr"/>
+      <c r="T87" s="7" t="inlineStr"/>
+      <c r="U87" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V87" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W87" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="26" customHeight="1">
+      <c r="A88" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>20260563747</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+      <c r="K88" s="7" t="inlineStr"/>
+      <c r="L88" s="7" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N88" s="7" t="inlineStr"/>
+      <c r="O88" s="7" t="inlineStr"/>
+      <c r="P88" s="7" t="inlineStr"/>
+      <c r="Q88" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R88" s="7" t="inlineStr"/>
+      <c r="S88" s="7" t="inlineStr"/>
+      <c r="T88" s="7" t="inlineStr"/>
+      <c r="U88" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V88" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W88" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>20260563748</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="7" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr"/>
+      <c r="L89" s="7" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr"/>
+      <c r="O89" s="7" t="inlineStr"/>
+      <c r="P89" s="7" t="inlineStr"/>
+      <c r="Q89" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R89" s="7" t="inlineStr"/>
+      <c r="S89" s="7" t="inlineStr"/>
+      <c r="T89" s="7" t="inlineStr"/>
+      <c r="U89" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V89" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W89" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>20260563749</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr"/>
+      <c r="J90" s="7" t="inlineStr"/>
+      <c r="K90" s="7" t="inlineStr"/>
+      <c r="L90" s="7" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr"/>
+      <c r="O90" s="7" t="inlineStr"/>
+      <c r="P90" s="7" t="inlineStr"/>
+      <c r="Q90" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R90" s="7" t="inlineStr"/>
+      <c r="S90" s="7" t="inlineStr"/>
+      <c r="T90" s="7" t="inlineStr"/>
+      <c r="U90" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V90" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W90" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>20260563750</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr"/>
+      <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr"/>
+      <c r="K91" s="7" t="inlineStr"/>
+      <c r="L91" s="7" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N91" s="7" t="inlineStr"/>
+      <c r="O91" s="7" t="inlineStr"/>
+      <c r="P91" s="7" t="inlineStr"/>
+      <c r="Q91" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R91" s="7" t="inlineStr"/>
+      <c r="S91" s="7" t="inlineStr"/>
+      <c r="T91" s="7" t="inlineStr"/>
+      <c r="U91" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V91" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W91" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>20260563751</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr"/>
+      <c r="H92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr"/>
+      <c r="J92" s="7" t="inlineStr"/>
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N92" s="7" t="inlineStr"/>
+      <c r="O92" s="7" t="inlineStr"/>
+      <c r="P92" s="7" t="inlineStr"/>
+      <c r="Q92" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R92" s="7" t="inlineStr"/>
+      <c r="S92" s="7" t="inlineStr"/>
+      <c r="T92" s="7" t="inlineStr"/>
+      <c r="U92" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V92" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W92" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>20260563752</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr"/>
+      <c r="J93" s="7" t="inlineStr"/>
+      <c r="K93" s="7" t="inlineStr"/>
+      <c r="L93" s="7" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="inlineStr"/>
+      <c r="O93" s="7" t="inlineStr"/>
+      <c r="P93" s="7" t="inlineStr"/>
+      <c r="Q93" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R93" s="7" t="inlineStr"/>
+      <c r="S93" s="7" t="inlineStr"/>
+      <c r="T93" s="7" t="inlineStr"/>
+      <c r="U93" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V93" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W93" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>20260563753</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr"/>
+      <c r="H94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr"/>
+      <c r="J94" s="7" t="inlineStr"/>
+      <c r="K94" s="7" t="inlineStr"/>
+      <c r="L94" s="7" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N94" s="7" t="inlineStr"/>
+      <c r="O94" s="7" t="inlineStr"/>
+      <c r="P94" s="7" t="inlineStr"/>
+      <c r="Q94" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R94" s="7" t="inlineStr"/>
+      <c r="S94" s="7" t="inlineStr"/>
+      <c r="T94" s="7" t="inlineStr"/>
+      <c r="U94" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V94" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W94" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>20260563754</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr"/>
+      <c r="K95" s="7" t="inlineStr"/>
+      <c r="L95" s="7" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr"/>
+      <c r="O95" s="7" t="inlineStr"/>
+      <c r="P95" s="7" t="inlineStr"/>
+      <c r="Q95" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R95" s="7" t="inlineStr"/>
+      <c r="S95" s="7" t="inlineStr"/>
+      <c r="T95" s="7" t="inlineStr"/>
+      <c r="U95" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V95" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W95" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>20260563755</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="7" t="inlineStr"/>
+      <c r="J96" s="7" t="inlineStr"/>
+      <c r="K96" s="7" t="inlineStr"/>
+      <c r="L96" s="7" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N96" s="7" t="inlineStr"/>
+      <c r="O96" s="7" t="inlineStr"/>
+      <c r="P96" s="7" t="inlineStr"/>
+      <c r="Q96" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R96" s="7" t="inlineStr"/>
+      <c r="S96" s="7" t="inlineStr"/>
+      <c r="T96" s="7" t="inlineStr"/>
+      <c r="U96" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V96" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W96" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="26" customHeight="1">
+      <c r="A97" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>20260563756</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr"/>
+      <c r="K97" s="7" t="inlineStr"/>
+      <c r="L97" s="7" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr"/>
+      <c r="O97" s="7" t="inlineStr"/>
+      <c r="P97" s="7" t="inlineStr"/>
+      <c r="Q97" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R97" s="7" t="inlineStr"/>
+      <c r="S97" s="7" t="inlineStr"/>
+      <c r="T97" s="7" t="inlineStr"/>
+      <c r="U97" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V97" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W97" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="26" customHeight="1">
+      <c r="A98" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>20260563757</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr"/>
+      <c r="H98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr"/>
+      <c r="J98" s="7" t="inlineStr"/>
+      <c r="K98" s="7" t="inlineStr"/>
+      <c r="L98" s="7" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N98" s="7" t="inlineStr"/>
+      <c r="O98" s="7" t="inlineStr"/>
+      <c r="P98" s="7" t="inlineStr"/>
+      <c r="Q98" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R98" s="7" t="inlineStr"/>
+      <c r="S98" s="7" t="inlineStr"/>
+      <c r="T98" s="7" t="inlineStr"/>
+      <c r="U98" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V98" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W98" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="26" customHeight="1">
+      <c r="A99" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>20260563758</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr"/>
+      <c r="K99" s="7" t="inlineStr"/>
+      <c r="L99" s="7" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr"/>
+      <c r="O99" s="7" t="inlineStr"/>
+      <c r="P99" s="7" t="inlineStr"/>
+      <c r="Q99" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R99" s="7" t="inlineStr"/>
+      <c r="S99" s="7" t="inlineStr"/>
+      <c r="T99" s="7" t="inlineStr"/>
+      <c r="U99" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V99" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W99" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="A100" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>20260563759</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr"/>
+      <c r="H100" s="7" t="inlineStr"/>
+      <c r="I100" s="7" t="inlineStr"/>
+      <c r="J100" s="7" t="inlineStr"/>
+      <c r="K100" s="7" t="inlineStr"/>
+      <c r="L100" s="7" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N100" s="7" t="inlineStr"/>
+      <c r="O100" s="7" t="inlineStr"/>
+      <c r="P100" s="7" t="inlineStr"/>
+      <c r="Q100" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R100" s="7" t="inlineStr"/>
+      <c r="S100" s="7" t="inlineStr"/>
+      <c r="T100" s="7" t="inlineStr"/>
+      <c r="U100" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V100" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W100" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="26" customHeight="1">
+      <c r="A101" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>20260563760</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr"/>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr"/>
+      <c r="J101" s="7" t="inlineStr"/>
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N101" s="7" t="inlineStr"/>
+      <c r="O101" s="7" t="inlineStr"/>
+      <c r="P101" s="7" t="inlineStr"/>
+      <c r="Q101" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R101" s="7" t="inlineStr"/>
+      <c r="S101" s="7" t="inlineStr"/>
+      <c r="T101" s="7" t="inlineStr"/>
+      <c r="U101" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V101" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W101" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="26" customHeight="1">
+      <c r="A102" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>20260563768</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr"/>
+      <c r="H102" s="7" t="inlineStr"/>
+      <c r="I102" s="7" t="inlineStr"/>
+      <c r="J102" s="7" t="inlineStr"/>
+      <c r="K102" s="7" t="inlineStr"/>
+      <c r="L102" s="7" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N102" s="7" t="inlineStr"/>
+      <c r="O102" s="7" t="inlineStr"/>
+      <c r="P102" s="7" t="inlineStr"/>
+      <c r="Q102" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R102" s="7" t="inlineStr"/>
+      <c r="S102" s="7" t="inlineStr"/>
+      <c r="T102" s="7" t="inlineStr"/>
+      <c r="U102" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V102" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W102" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="26" customHeight="1">
+      <c r="A103" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>20260563769</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr"/>
+      <c r="G103" s="7" t="inlineStr"/>
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr"/>
+      <c r="J103" s="7" t="inlineStr"/>
+      <c r="K103" s="7" t="inlineStr"/>
+      <c r="L103" s="7" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N103" s="7" t="inlineStr"/>
+      <c r="O103" s="7" t="inlineStr"/>
+      <c r="P103" s="7" t="inlineStr"/>
+      <c r="Q103" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R103" s="7" t="inlineStr"/>
+      <c r="S103" s="7" t="inlineStr"/>
+      <c r="T103" s="7" t="inlineStr"/>
+      <c r="U103" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V103" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W103" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="26" customHeight="1">
+      <c r="A104" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>20260563771</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr"/>
+      <c r="K104" s="7" t="inlineStr"/>
+      <c r="L104" s="7" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N104" s="7" t="inlineStr"/>
+      <c r="O104" s="7" t="inlineStr"/>
+      <c r="P104" s="7" t="inlineStr"/>
+      <c r="Q104" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R104" s="7" t="inlineStr"/>
+      <c r="S104" s="7" t="inlineStr"/>
+      <c r="T104" s="7" t="inlineStr"/>
+      <c r="U104" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V104" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W104" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="26" customHeight="1">
+      <c r="A105" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>20260563786</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr"/>
+      <c r="I105" s="7" t="inlineStr"/>
+      <c r="J105" s="7" t="inlineStr"/>
+      <c r="K105" s="7" t="inlineStr"/>
+      <c r="L105" s="7" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N105" s="7" t="inlineStr"/>
+      <c r="O105" s="7" t="inlineStr"/>
+      <c r="P105" s="7" t="inlineStr"/>
+      <c r="Q105" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R105" s="7" t="inlineStr"/>
+      <c r="S105" s="7" t="inlineStr"/>
+      <c r="T105" s="7" t="inlineStr"/>
+      <c r="U105" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V105" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W105" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="26" customHeight="1">
+      <c r="A106" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>20260563787</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr"/>
+      <c r="G106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="7" t="inlineStr"/>
+      <c r="J106" s="7" t="inlineStr"/>
+      <c r="K106" s="7" t="inlineStr"/>
+      <c r="L106" s="7" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N106" s="7" t="inlineStr"/>
+      <c r="O106" s="7" t="inlineStr"/>
+      <c r="P106" s="7" t="inlineStr"/>
+      <c r="Q106" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R106" s="7" t="inlineStr"/>
+      <c r="S106" s="7" t="inlineStr"/>
+      <c r="T106" s="7" t="inlineStr"/>
+      <c r="U106" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V106" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W106" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="26" customHeight="1">
+      <c r="A107" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>20260563790</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr"/>
+      <c r="G107" s="7" t="inlineStr"/>
+      <c r="H107" s="7" t="inlineStr"/>
+      <c r="I107" s="7" t="inlineStr"/>
+      <c r="J107" s="7" t="inlineStr"/>
+      <c r="K107" s="7" t="inlineStr"/>
+      <c r="L107" s="7" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N107" s="7" t="inlineStr"/>
+      <c r="O107" s="7" t="inlineStr"/>
+      <c r="P107" s="7" t="inlineStr"/>
+      <c r="Q107" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R107" s="7" t="inlineStr"/>
+      <c r="S107" s="7" t="inlineStr"/>
+      <c r="T107" s="7" t="inlineStr"/>
+      <c r="U107" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V107" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W107" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="26" customHeight="1">
+      <c r="A108" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>20260563793</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr"/>
+      <c r="I108" s="7" t="inlineStr"/>
+      <c r="J108" s="7" t="inlineStr"/>
+      <c r="K108" s="7" t="inlineStr"/>
+      <c r="L108" s="7" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N108" s="7" t="inlineStr"/>
+      <c r="O108" s="7" t="inlineStr"/>
+      <c r="P108" s="7" t="inlineStr"/>
+      <c r="Q108" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R108" s="7" t="inlineStr"/>
+      <c r="S108" s="7" t="inlineStr"/>
+      <c r="T108" s="7" t="inlineStr"/>
+      <c r="U108" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V108" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W108" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="26" customHeight="1">
+      <c r="A109" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>20260563796</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr"/>
+      <c r="H109" s="7" t="inlineStr"/>
+      <c r="I109" s="7" t="inlineStr"/>
+      <c r="J109" s="7" t="inlineStr"/>
+      <c r="K109" s="7" t="inlineStr"/>
+      <c r="L109" s="7" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N109" s="7" t="inlineStr"/>
+      <c r="O109" s="7" t="inlineStr"/>
+      <c r="P109" s="7" t="inlineStr"/>
+      <c r="Q109" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R109" s="7" t="inlineStr"/>
+      <c r="S109" s="7" t="inlineStr"/>
+      <c r="T109" s="7" t="inlineStr"/>
+      <c r="U109" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V109" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W109" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="26" customHeight="1">
+      <c r="A110" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>20260563802</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr"/>
+      <c r="G110" s="7" t="inlineStr"/>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="7" t="inlineStr"/>
+      <c r="J110" s="7" t="inlineStr"/>
+      <c r="K110" s="7" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N110" s="7" t="inlineStr"/>
+      <c r="O110" s="7" t="inlineStr"/>
+      <c r="P110" s="7" t="inlineStr"/>
+      <c r="Q110" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R110" s="7" t="inlineStr"/>
+      <c r="S110" s="7" t="inlineStr"/>
+      <c r="T110" s="7" t="inlineStr"/>
+      <c r="U110" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V110" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W110" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="26" customHeight="1">
+      <c r="A111" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>20260563996</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr"/>
+      <c r="G111" s="7" t="inlineStr"/>
+      <c r="H111" s="7" t="inlineStr"/>
+      <c r="I111" s="7" t="inlineStr"/>
+      <c r="J111" s="7" t="inlineStr"/>
+      <c r="K111" s="7" t="inlineStr"/>
+      <c r="L111" s="7" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N111" s="7" t="inlineStr"/>
+      <c r="O111" s="7" t="inlineStr"/>
+      <c r="P111" s="7" t="inlineStr"/>
+      <c r="Q111" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R111" s="7" t="inlineStr"/>
+      <c r="S111" s="7" t="inlineStr"/>
+      <c r="T111" s="7" t="inlineStr"/>
+      <c r="U111" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V111" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W111" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>20260564007</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr"/>
+      <c r="G112" s="7" t="inlineStr"/>
+      <c r="H112" s="7" t="inlineStr"/>
+      <c r="I112" s="7" t="inlineStr"/>
+      <c r="J112" s="7" t="inlineStr"/>
+      <c r="K112" s="7" t="inlineStr"/>
+      <c r="L112" s="7" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N112" s="7" t="inlineStr"/>
+      <c r="O112" s="7" t="inlineStr"/>
+      <c r="P112" s="7" t="inlineStr"/>
+      <c r="Q112" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R112" s="7" t="inlineStr"/>
+      <c r="S112" s="7" t="inlineStr"/>
+      <c r="T112" s="7" t="inlineStr"/>
+      <c r="U112" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V112" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W112" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>20260564068</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr"/>
+      <c r="H113" s="7" t="inlineStr"/>
+      <c r="I113" s="7" t="inlineStr"/>
+      <c r="J113" s="7" t="inlineStr"/>
+      <c r="K113" s="7" t="inlineStr"/>
+      <c r="L113" s="7" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N113" s="7" t="inlineStr"/>
+      <c r="O113" s="7" t="inlineStr"/>
+      <c r="P113" s="7" t="inlineStr"/>
+      <c r="Q113" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R113" s="7" t="inlineStr"/>
+      <c r="S113" s="7" t="inlineStr"/>
+      <c r="T113" s="7" t="inlineStr"/>
+      <c r="U113" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V113" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W113" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="26" customHeight="1">
+      <c r="A114" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>20260564146</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr"/>
+      <c r="G114" s="7" t="inlineStr"/>
+      <c r="H114" s="7" t="inlineStr"/>
+      <c r="I114" s="7" t="inlineStr"/>
+      <c r="J114" s="7" t="inlineStr"/>
+      <c r="K114" s="7" t="inlineStr"/>
+      <c r="L114" s="7" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N114" s="7" t="inlineStr"/>
+      <c r="O114" s="7" t="inlineStr"/>
+      <c r="P114" s="7" t="inlineStr"/>
+      <c r="Q114" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R114" s="7" t="inlineStr"/>
+      <c r="S114" s="7" t="inlineStr"/>
+      <c r="T114" s="7" t="inlineStr"/>
+      <c r="U114" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V114" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W114" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="26" customHeight="1">
+      <c r="A115" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>20260564592</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr"/>
+      <c r="G115" s="7" t="inlineStr"/>
+      <c r="H115" s="7" t="inlineStr"/>
+      <c r="I115" s="7" t="inlineStr"/>
+      <c r="J115" s="7" t="inlineStr"/>
+      <c r="K115" s="7" t="inlineStr"/>
+      <c r="L115" s="7" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N115" s="7" t="inlineStr"/>
+      <c r="O115" s="7" t="inlineStr"/>
+      <c r="P115" s="7" t="inlineStr"/>
+      <c r="Q115" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R115" s="7" t="inlineStr"/>
+      <c r="S115" s="7" t="inlineStr"/>
+      <c r="T115" s="7" t="inlineStr"/>
+      <c r="U115" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V115" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W115" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="26" customHeight="1">
+      <c r="A116" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>20260564594</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr"/>
+      <c r="G116" s="7" t="inlineStr"/>
+      <c r="H116" s="7" t="inlineStr"/>
+      <c r="I116" s="7" t="inlineStr"/>
+      <c r="J116" s="7" t="inlineStr"/>
+      <c r="K116" s="7" t="inlineStr"/>
+      <c r="L116" s="7" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N116" s="7" t="inlineStr"/>
+      <c r="O116" s="7" t="inlineStr"/>
+      <c r="P116" s="7" t="inlineStr"/>
+      <c r="Q116" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R116" s="7" t="inlineStr"/>
+      <c r="S116" s="7" t="inlineStr"/>
+      <c r="T116" s="7" t="inlineStr"/>
+      <c r="U116" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V116" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W116" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="26" customHeight="1">
+      <c r="A117" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>20260564731</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr"/>
+      <c r="G117" s="7" t="inlineStr"/>
+      <c r="H117" s="7" t="inlineStr"/>
+      <c r="I117" s="7" t="inlineStr"/>
+      <c r="J117" s="7" t="inlineStr"/>
+      <c r="K117" s="7" t="inlineStr"/>
+      <c r="L117" s="7" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N117" s="7" t="inlineStr"/>
+      <c r="O117" s="7" t="inlineStr"/>
+      <c r="P117" s="7" t="inlineStr"/>
+      <c r="Q117" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R117" s="7" t="inlineStr"/>
+      <c r="S117" s="7" t="inlineStr"/>
+      <c r="T117" s="7" t="inlineStr"/>
+      <c r="U117" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V117" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W117" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="26" customHeight="1">
+      <c r="A118" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>20260564732</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr"/>
+      <c r="G118" s="7" t="inlineStr"/>
+      <c r="H118" s="7" t="inlineStr"/>
+      <c r="I118" s="7" t="inlineStr"/>
+      <c r="J118" s="7" t="inlineStr"/>
+      <c r="K118" s="7" t="inlineStr"/>
+      <c r="L118" s="7" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N118" s="7" t="inlineStr"/>
+      <c r="O118" s="7" t="inlineStr"/>
+      <c r="P118" s="7" t="inlineStr"/>
+      <c r="Q118" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R118" s="7" t="inlineStr"/>
+      <c r="S118" s="7" t="inlineStr"/>
+      <c r="T118" s="7" t="inlineStr"/>
+      <c r="U118" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V118" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W118" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="26" customHeight="1">
+      <c r="A119" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>20260564734</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr"/>
+      <c r="G119" s="7" t="inlineStr"/>
+      <c r="H119" s="7" t="inlineStr"/>
+      <c r="I119" s="7" t="inlineStr"/>
+      <c r="J119" s="7" t="inlineStr"/>
+      <c r="K119" s="7" t="inlineStr"/>
+      <c r="L119" s="7" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N119" s="7" t="inlineStr"/>
+      <c r="O119" s="7" t="inlineStr"/>
+      <c r="P119" s="7" t="inlineStr"/>
+      <c r="Q119" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R119" s="7" t="inlineStr"/>
+      <c r="S119" s="7" t="inlineStr"/>
+      <c r="T119" s="7" t="inlineStr"/>
+      <c r="U119" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V119" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W119" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="26" customHeight="1">
+      <c r="A120" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>20260565086</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr"/>
+      <c r="G120" s="7" t="inlineStr"/>
+      <c r="H120" s="7" t="inlineStr"/>
+      <c r="I120" s="7" t="inlineStr"/>
+      <c r="J120" s="7" t="inlineStr"/>
+      <c r="K120" s="7" t="inlineStr"/>
+      <c r="L120" s="7" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N120" s="7" t="inlineStr"/>
+      <c r="O120" s="7" t="inlineStr"/>
+      <c r="P120" s="7" t="inlineStr"/>
+      <c r="Q120" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R120" s="7" t="inlineStr"/>
+      <c r="S120" s="7" t="inlineStr"/>
+      <c r="T120" s="7" t="inlineStr"/>
+      <c r="U120" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V120" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W120" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="26" customHeight="1">
+      <c r="A121" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>20260565087</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr"/>
+      <c r="G121" s="7" t="inlineStr"/>
+      <c r="H121" s="7" t="inlineStr"/>
+      <c r="I121" s="7" t="inlineStr"/>
+      <c r="J121" s="7" t="inlineStr"/>
+      <c r="K121" s="7" t="inlineStr"/>
+      <c r="L121" s="7" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N121" s="7" t="inlineStr"/>
+      <c r="O121" s="7" t="inlineStr"/>
+      <c r="P121" s="7" t="inlineStr"/>
+      <c r="Q121" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R121" s="7" t="inlineStr"/>
+      <c r="S121" s="7" t="inlineStr"/>
+      <c r="T121" s="7" t="inlineStr"/>
+      <c r="U121" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V121" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W121" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="26" customHeight="1">
+      <c r="A122" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>20260565088</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr"/>
+      <c r="G122" s="7" t="inlineStr"/>
+      <c r="H122" s="7" t="inlineStr"/>
+      <c r="I122" s="7" t="inlineStr"/>
+      <c r="J122" s="7" t="inlineStr"/>
+      <c r="K122" s="7" t="inlineStr"/>
+      <c r="L122" s="7" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N122" s="7" t="inlineStr"/>
+      <c r="O122" s="7" t="inlineStr"/>
+      <c r="P122" s="7" t="inlineStr"/>
+      <c r="Q122" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R122" s="7" t="inlineStr"/>
+      <c r="S122" s="7" t="inlineStr"/>
+      <c r="T122" s="7" t="inlineStr"/>
+      <c r="U122" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V122" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W122" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="26" customHeight="1">
+      <c r="A123" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>20260565466</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr"/>
+      <c r="G123" s="7" t="inlineStr"/>
+      <c r="H123" s="7" t="inlineStr"/>
+      <c r="I123" s="7" t="inlineStr"/>
+      <c r="J123" s="7" t="inlineStr"/>
+      <c r="K123" s="7" t="inlineStr"/>
+      <c r="L123" s="7" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N123" s="7" t="inlineStr"/>
+      <c r="O123" s="7" t="inlineStr"/>
+      <c r="P123" s="7" t="inlineStr"/>
+      <c r="Q123" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R123" s="7" t="inlineStr"/>
+      <c r="S123" s="7" t="inlineStr"/>
+      <c r="T123" s="7" t="inlineStr"/>
+      <c r="U123" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V123" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W123" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="26" customHeight="1">
+      <c r="A124" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>20260565623</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr"/>
+      <c r="G124" s="7" t="inlineStr"/>
+      <c r="H124" s="7" t="inlineStr"/>
+      <c r="I124" s="7" t="inlineStr"/>
+      <c r="J124" s="7" t="inlineStr"/>
+      <c r="K124" s="7" t="inlineStr"/>
+      <c r="L124" s="7" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N124" s="7" t="inlineStr"/>
+      <c r="O124" s="7" t="inlineStr"/>
+      <c r="P124" s="7" t="inlineStr"/>
+      <c r="Q124" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R124" s="7" t="inlineStr"/>
+      <c r="S124" s="7" t="inlineStr"/>
+      <c r="T124" s="7" t="inlineStr"/>
+      <c r="U124" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V124" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W124" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="26" customHeight="1">
+      <c r="A125" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>20260566223</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr"/>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr"/>
+      <c r="I125" s="7" t="inlineStr"/>
+      <c r="J125" s="7" t="inlineStr"/>
+      <c r="K125" s="7" t="inlineStr"/>
+      <c r="L125" s="7" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N125" s="7" t="inlineStr"/>
+      <c r="O125" s="7" t="inlineStr"/>
+      <c r="P125" s="7" t="inlineStr"/>
+      <c r="Q125" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R125" s="7" t="inlineStr"/>
+      <c r="S125" s="7" t="inlineStr"/>
+      <c r="T125" s="7" t="inlineStr"/>
+      <c r="U125" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V125" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W125" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="26" customHeight="1">
+      <c r="A126" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>20260566224</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr"/>
+      <c r="F126" s="7" t="inlineStr"/>
+      <c r="G126" s="7" t="inlineStr"/>
+      <c r="H126" s="7" t="inlineStr"/>
+      <c r="I126" s="7" t="inlineStr"/>
+      <c r="J126" s="7" t="inlineStr"/>
+      <c r="K126" s="7" t="inlineStr"/>
+      <c r="L126" s="7" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N126" s="7" t="inlineStr"/>
+      <c r="O126" s="7" t="inlineStr"/>
+      <c r="P126" s="7" t="inlineStr"/>
+      <c r="Q126" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R126" s="7" t="inlineStr"/>
+      <c r="S126" s="7" t="inlineStr"/>
+      <c r="T126" s="7" t="inlineStr"/>
+      <c r="U126" s="7" t="inlineStr">
+        <is>
+          <t>Medical lien</t>
+        </is>
+      </c>
+      <c r="V126" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W126" s="8" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W126"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W126" r:id="rId125"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -618,7 +8866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -626,7 +8874,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -635,88 +8883,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-09-28 06:27</t>
+          <t>Run: 2026-09-29 06:41</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="A3" s="10" t="inlineStr"/>
+      <c r="B3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="10" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>With Property Address</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>With Mailing Address</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>With Property Address</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>PDF Parsed</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Score 70+ (Hot)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>With Mailing Address</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>PDF Parsed</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Score 70+ (Hot)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Score 50-69 (Warm)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
+      <c r="B9" s="10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" s="10" t="inlineStr"/>
+      <c r="B10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>By Category</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,22 +37,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00374151"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="002563EB"/>
-      <sz val="9"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
@@ -65,7 +49,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -75,11 +59,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2433"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,23 +88,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -636,418 +606,8 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Probate Document</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>20260574924</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Probate / estate; New this week</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Probate Document</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>20260573920</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>Probate / estate; New this week</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Probate Document</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>20260574216</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT :</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>Probate / estate; New this week</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Probate Document</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>20260574640</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>Probate / estate; New this week</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Probate Document</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>20260574678</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>Probate / estate; New this week</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Probate Document</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>20260575012</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>Probate / estate; New this week</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W7"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId6"/>
-  </hyperlinks>
+  <autoFilter ref="A1:W1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1058,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1066,7 +626,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -1075,98 +635,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-02 06:45</t>
+          <t>Run: 2026-10-03 06:08</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>6</v>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>With Property Address</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>With Mailing Address</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>PDF Parsed</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>6</v>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Score 70+ (Hot)</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Score 50-69 (Warm)</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>By Category</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Probate Document</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-03 06:08</t>
+          <t>Run: 2026-10-04 06:36</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-04 06:36</t>
+          <t>Run: 2026-10-05 06:32</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-05 06:32</t>
+          <t>Run: 2026-10-06 07:17</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,22 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00374151"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
@@ -49,7 +65,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +75,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2433"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,14 +109,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -606,8 +636,342 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>20260580703</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court of the State of</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>20260581668</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>20260581686</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>VICKI L. LESCOE</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>20260581770</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>503-50-558</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>20260581804</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W6"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -618,7 +982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -626,7 +990,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -635,88 +999,98 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-06 07:17</t>
+          <t>Run: 2026-10-07 06:57</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="A3" s="6" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>With Property Address</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>With Property Address</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>With Mailing Address</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>With Mailing Address</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>PDF Parsed</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Score 70+ (Hot)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>PDF Parsed</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Score 50-69 (Warm)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Score 70+ (Hot)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Score 50-69 (Warm)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>By Category</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,7 +39,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00374151"/>
+      <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -46,9 +48,26 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="002563EB"/>
       <sz val="9"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00374151"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -65,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +94,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2433"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -120,12 +149,36 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -638,45 +691,71 @@
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>20260580703</t>
+          <t>20260582119</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>CHARLES A QUINN AND LISA M QUINN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>ROCKET MORTGAGE, LLC</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>294880</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Superior Court of the State of</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>Superior Court Building Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>3029 W PARADISE DR</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>85029</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" s="3" t="inlineStr">
@@ -686,10 +765,14 @@
       </c>
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>America West Lender Services, LLC</t>
+        </is>
+      </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
@@ -697,7 +780,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="W2" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -705,41 +788,71 @@
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="2" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>20260581668</t>
+          <t>20260582301</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ROSS BENEDETTO, SURVIVING SPOUSE OF BEVERLY BENEDETTO, WHO PASSED AWAY ON</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>338402</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>4946 W CHARLESTON AVE</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
@@ -748,11 +861,19 @@
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>207-23-34902</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
@@ -760,7 +881,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -768,45 +889,71 @@
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>20260581686</t>
+          <t>20260582308</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>CHRISTOPHER STOKES AND KIMBERLY STOKES</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>VICKI L. LESCOE</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>473398</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>30182 WEST MULBERRY DRIVE</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>85396</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
@@ -815,11 +962,19 @@
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>504-74-5427</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
@@ -827,7 +982,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -835,41 +990,71 @@
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>20260581770</t>
+          <t>20260582458</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>NICHOLAS QUINTON HAYES AND TINA SUK HAYES</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>459685</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>1015 S 150TH DR</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
@@ -880,13 +1065,17 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>503-50-558</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr"/>
+          <t>500-10-32792</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -894,7 +1083,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="W5" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -902,41 +1091,71 @@
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>20260581804</t>
+          <t>20260582614</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>JEAN C. HABINEZA</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>525299</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>9441 W HEATHERBRAE DR</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>85037</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
@@ -945,32 +1164,3744 @@
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>102-25-54952</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>20260582840</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>CINDY M CORRAL</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>473259</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>12540 W TRUMBULL RD</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>AVONDALE</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>500-72-13512</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>20260583265</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Dalton Etherton</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>551610</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>1200 S Sunset Dr</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>303-27-7888</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>20260583698</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Miguel Aguirre</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>330382</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>1822 E Diamond St</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>116-12-067</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>20260584023</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>TSZYU JARED ZAVALA</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>168884</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>6302 N 64TH DR 4</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>144-15-047</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>20260584175</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>MARINO MASCARENAS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>NEWREZ LLC</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>262500</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>2424 N 114TH LN</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>AVONDALE</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>85392</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>Prime Recon LLC</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>20260582345</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>PATINA MUHAMMAD;</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association, not in its individual capacity, but solely as owner trustee of the New Residential</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>518059</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>2027-01-28</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr"/>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr"/>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>102-56-4399</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>Michelle R. Ghidotti, Esq.</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>20260582829</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>C/O Click N’ Close, Inc. FKA Mid America</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>37632200</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>220-36-137</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr"/>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>20260583065</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>C/O MidFirst Bank</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>117978</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr"/>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr"/>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>148-12-1201</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr"/>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>20260583066</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="n">
+        <v>335620</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>143-49-486</t>
+        </is>
+      </c>
+      <c r="T15" s="7" t="inlineStr"/>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>20260583178</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>MOONSHOT HOLDINGS, LLC AN ARIZONA LIMITED LIABILITY COMPANY</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Wilmington Trust, National Association not in its individual capacity but solely as Trustee of Endea</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>248500</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>218-54-717</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>20260583391</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>C/O MidFirst Bank</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>466396</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr"/>
+      <c r="O17" s="7" t="inlineStr"/>
+      <c r="P17" s="7" t="inlineStr"/>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr"/>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>508-07-495</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr"/>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>20260583392</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>C/O MidFirst Bank</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>417000</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>211-67-037</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr"/>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>20260583632</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>C/O LoanCare, LLC</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>429322</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr"/>
+      <c r="O19" s="7" t="inlineStr"/>
+      <c r="P19" s="7" t="inlineStr"/>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr"/>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>102-56-4560</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr"/>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>20260583633</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>C/O LoanCare, LLC</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>359370</v>
+      </c>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr"/>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr"/>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>102-30-590</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr"/>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>20260583688</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Luis Orozco</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>51000</v>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>513 W Colgate Dr</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>301-04-3880</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>20260583912</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="8" t="n">
+        <v>126750</v>
+      </c>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>149-41-1182</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr"/>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>20260583914</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>C/O NewRez LLC, d/b/a Shellpoint Mortgage</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>215000</v>
+      </c>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>104-90-183</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr"/>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>20260583917</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>C/O NewRez LLC, d/b/a Shellpoint Mortgage</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>385000</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr"/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>138-14-014</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr"/>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>20260584072</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="8" t="n">
+        <v>700000</v>
+      </c>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING AT 201 W JEFFERSON</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>219-38-007</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>20260584073</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="8" t="n">
+        <v>158950</v>
+      </c>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING AT 201 W JEFFERSON</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr"/>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr"/>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>105-70-047</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr"/>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>20260584074</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="8" t="n">
+        <v>228450</v>
+      </c>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING AT 201 W JEFFERSON</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr"/>
+      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr"/>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr"/>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>109-44-054</t>
+        </is>
+      </c>
+      <c r="T27" s="7" t="inlineStr"/>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>20260584191</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>NICHOLAS BARRY LACONTE</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="8" t="n">
+        <v>124500</v>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr"/>
+      <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr"/>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr"/>
+      <c r="S28" s="7" t="inlineStr"/>
+      <c r="T28" s="7" t="inlineStr">
+        <is>
+          <t>Prime Recon LLC</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>20260584150</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>26213 North 121% Lane</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>85383</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr"/>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr"/>
+      <c r="S29" s="7" t="inlineStr"/>
+      <c r="T29" s="7" t="inlineStr"/>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>20260582145</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>6610 E ROLAND STREET</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>85215</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr"/>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr"/>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>141-69-683</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="inlineStr"/>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
           <t>Tax deed; New this week</t>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="V30" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>20260582098</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr"/>
+      <c r="G31" s="11" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr"/>
+      <c r="I31" s="11" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr"/>
+      <c r="L31" s="11" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr"/>
+      <c r="O31" s="11" t="inlineStr"/>
+      <c r="P31" s="11" t="inlineStr"/>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R31" s="11" t="inlineStr"/>
+      <c r="S31" s="11" t="inlineStr"/>
+      <c r="T31" s="11" t="inlineStr"/>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>20260582099</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr"/>
+      <c r="G32" s="11" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr"/>
+      <c r="I32" s="11" t="inlineStr"/>
+      <c r="J32" s="11" t="inlineStr"/>
+      <c r="K32" s="11" t="inlineStr"/>
+      <c r="L32" s="11" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N32" s="11" t="inlineStr"/>
+      <c r="O32" s="11" t="inlineStr"/>
+      <c r="P32" s="11" t="inlineStr"/>
+      <c r="Q32" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R32" s="11" t="inlineStr"/>
+      <c r="S32" s="11" t="inlineStr"/>
+      <c r="T32" s="11" t="inlineStr"/>
+      <c r="U32" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V32" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W32" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>20260582473</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr"/>
+      <c r="G33" s="11" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr"/>
+      <c r="I33" s="11" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr"/>
+      <c r="L33" s="11" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr"/>
+      <c r="O33" s="11" t="inlineStr"/>
+      <c r="P33" s="11" t="inlineStr"/>
+      <c r="Q33" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R33" s="11" t="inlineStr"/>
+      <c r="S33" s="11" t="inlineStr"/>
+      <c r="T33" s="11" t="inlineStr"/>
+      <c r="U33" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>20260582647</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
+      <c r="G34" s="11" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr"/>
+      <c r="L34" s="11" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N34" s="11" t="inlineStr"/>
+      <c r="O34" s="11" t="inlineStr"/>
+      <c r="P34" s="11" t="inlineStr"/>
+      <c r="Q34" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R34" s="11" t="inlineStr"/>
+      <c r="S34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="inlineStr"/>
+      <c r="U34" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>20260582654</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="11" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr"/>
+      <c r="L35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr"/>
+      <c r="O35" s="11" t="inlineStr"/>
+      <c r="P35" s="11" t="inlineStr"/>
+      <c r="Q35" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R35" s="11" t="inlineStr"/>
+      <c r="S35" s="11" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr"/>
+      <c r="U35" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V35" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>20260582663</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr"/>
+      <c r="G36" s="11" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr"/>
+      <c r="I36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr"/>
+      <c r="L36" s="11" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N36" s="11" t="inlineStr"/>
+      <c r="O36" s="11" t="inlineStr"/>
+      <c r="P36" s="11" t="inlineStr"/>
+      <c r="Q36" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R36" s="11" t="inlineStr"/>
+      <c r="S36" s="11" t="inlineStr"/>
+      <c r="T36" s="11" t="inlineStr"/>
+      <c r="U36" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V36" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W36" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>20260582683</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
+      <c r="G37" s="11" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr"/>
+      <c r="I37" s="11" t="inlineStr"/>
+      <c r="J37" s="11" t="inlineStr"/>
+      <c r="K37" s="11" t="inlineStr"/>
+      <c r="L37" s="11" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr"/>
+      <c r="O37" s="11" t="inlineStr"/>
+      <c r="P37" s="11" t="inlineStr"/>
+      <c r="Q37" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R37" s="11" t="inlineStr"/>
+      <c r="S37" s="11" t="inlineStr"/>
+      <c r="T37" s="11" t="inlineStr"/>
+      <c r="U37" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V37" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>20260582693</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr"/>
+      <c r="G38" s="11" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr"/>
+      <c r="I38" s="11" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr"/>
+      <c r="L38" s="11" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N38" s="11" t="inlineStr"/>
+      <c r="O38" s="11" t="inlineStr"/>
+      <c r="P38" s="11" t="inlineStr"/>
+      <c r="Q38" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R38" s="11" t="inlineStr"/>
+      <c r="S38" s="11" t="inlineStr"/>
+      <c r="T38" s="11" t="inlineStr"/>
+      <c r="U38" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V38" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W38" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>20260582694</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr"/>
+      <c r="I39" s="11" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr"/>
+      <c r="K39" s="11" t="inlineStr"/>
+      <c r="L39" s="11" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr"/>
+      <c r="O39" s="11" t="inlineStr"/>
+      <c r="P39" s="11" t="inlineStr"/>
+      <c r="Q39" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R39" s="11" t="inlineStr"/>
+      <c r="S39" s="11" t="inlineStr"/>
+      <c r="T39" s="11" t="inlineStr"/>
+      <c r="U39" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V39" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W39" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>20260582709</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr"/>
+      <c r="G40" s="11" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr"/>
+      <c r="I40" s="11" t="inlineStr"/>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
+      <c r="L40" s="11" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N40" s="11" t="inlineStr"/>
+      <c r="O40" s="11" t="inlineStr"/>
+      <c r="P40" s="11" t="inlineStr"/>
+      <c r="Q40" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R40" s="11" t="inlineStr"/>
+      <c r="S40" s="11" t="inlineStr"/>
+      <c r="T40" s="11" t="inlineStr"/>
+      <c r="U40" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V40" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W40" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>20260582723</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
+      <c r="I41" s="11" t="inlineStr"/>
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr"/>
+      <c r="L41" s="11" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr"/>
+      <c r="O41" s="11" t="inlineStr"/>
+      <c r="P41" s="11" t="inlineStr"/>
+      <c r="Q41" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R41" s="11" t="inlineStr"/>
+      <c r="S41" s="11" t="inlineStr"/>
+      <c r="T41" s="11" t="inlineStr"/>
+      <c r="U41" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V41" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W41" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>20260582744</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr"/>
+      <c r="G42" s="11" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr"/>
+      <c r="I42" s="11" t="inlineStr"/>
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr"/>
+      <c r="L42" s="11" t="inlineStr"/>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N42" s="11" t="inlineStr"/>
+      <c r="O42" s="11" t="inlineStr"/>
+      <c r="P42" s="11" t="inlineStr"/>
+      <c r="Q42" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R42" s="11" t="inlineStr"/>
+      <c r="S42" s="11" t="inlineStr"/>
+      <c r="T42" s="11" t="inlineStr"/>
+      <c r="U42" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V42" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>20260582749</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr"/>
+      <c r="I43" s="11" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr"/>
+      <c r="L43" s="11" t="inlineStr"/>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr"/>
+      <c r="O43" s="11" t="inlineStr"/>
+      <c r="P43" s="11" t="inlineStr"/>
+      <c r="Q43" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R43" s="11" t="inlineStr"/>
+      <c r="S43" s="11" t="inlineStr"/>
+      <c r="T43" s="11" t="inlineStr"/>
+      <c r="U43" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V43" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W43" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>20260582811</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr"/>
+      <c r="G44" s="11" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr"/>
+      <c r="I44" s="11" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court of the State of Arizona</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr"/>
+      <c r="L44" s="11" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr"/>
+      <c r="O44" s="11" t="inlineStr"/>
+      <c r="P44" s="11" t="inlineStr"/>
+      <c r="Q44" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R44" s="11" t="inlineStr"/>
+      <c r="S44" s="11" t="inlineStr"/>
+      <c r="T44" s="11" t="inlineStr"/>
+      <c r="U44" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V44" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>20260583156</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr"/>
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr"/>
+      <c r="I45" s="11" t="inlineStr"/>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr"/>
+      <c r="L45" s="11" t="inlineStr"/>
+      <c r="M45" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr"/>
+      <c r="O45" s="11" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr"/>
+      <c r="Q45" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R45" s="11" t="inlineStr"/>
+      <c r="S45" s="11" t="inlineStr"/>
+      <c r="T45" s="11" t="inlineStr"/>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V45" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W45" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>20260583157</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr"/>
+      <c r="G46" s="11" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr"/>
+      <c r="I46" s="11" t="inlineStr"/>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr"/>
+      <c r="L46" s="11" t="inlineStr"/>
+      <c r="M46" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N46" s="11" t="inlineStr"/>
+      <c r="O46" s="11" t="inlineStr"/>
+      <c r="P46" s="11" t="inlineStr"/>
+      <c r="Q46" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R46" s="11" t="inlineStr"/>
+      <c r="S46" s="11" t="inlineStr"/>
+      <c r="T46" s="11" t="inlineStr"/>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V46" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W46" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>20260583628</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr"/>
+      <c r="I47" s="11" t="inlineStr"/>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr"/>
+      <c r="L47" s="11" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr"/>
+      <c r="O47" s="11" t="inlineStr"/>
+      <c r="P47" s="11" t="inlineStr"/>
+      <c r="Q47" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R47" s="11" t="inlineStr"/>
+      <c r="S47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="inlineStr"/>
+      <c r="U47" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V47" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W47" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>20260583713</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr"/>
+      <c r="I48" s="11" t="inlineStr"/>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="inlineStr"/>
+      <c r="L48" s="11" t="inlineStr"/>
+      <c r="M48" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N48" s="11" t="inlineStr"/>
+      <c r="O48" s="11" t="inlineStr"/>
+      <c r="P48" s="11" t="inlineStr"/>
+      <c r="Q48" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R48" s="11" t="inlineStr"/>
+      <c r="S48" s="11" t="inlineStr"/>
+      <c r="T48" s="11" t="inlineStr"/>
+      <c r="U48" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V48" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W48" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>20260584042</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr"/>
+      <c r="G49" s="11" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr"/>
+      <c r="I49" s="11" t="inlineStr"/>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr"/>
+      <c r="L49" s="11" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr"/>
+      <c r="O49" s="11" t="inlineStr"/>
+      <c r="P49" s="11" t="inlineStr"/>
+      <c r="Q49" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R49" s="11" t="inlineStr"/>
+      <c r="S49" s="11" t="inlineStr"/>
+      <c r="T49" s="11" t="inlineStr"/>
+      <c r="U49" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V49" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W49" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>20260584114</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr"/>
+      <c r="G50" s="11" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr"/>
+      <c r="I50" s="11" t="inlineStr"/>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr"/>
+      <c r="L50" s="11" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N50" s="11" t="inlineStr"/>
+      <c r="O50" s="11" t="inlineStr"/>
+      <c r="P50" s="11" t="inlineStr"/>
+      <c r="Q50" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R50" s="11" t="inlineStr"/>
+      <c r="S50" s="11" t="inlineStr"/>
+      <c r="T50" s="11" t="inlineStr"/>
+      <c r="U50" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V50" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>20260584186</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr"/>
+      <c r="I51" s="11" t="inlineStr"/>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr"/>
+      <c r="L51" s="11" t="inlineStr"/>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr"/>
+      <c r="O51" s="11" t="inlineStr"/>
+      <c r="P51" s="11" t="inlineStr"/>
+      <c r="Q51" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R51" s="11" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
+      <c r="U51" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W51" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>20260582107</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr"/>
+      <c r="G52" s="11" t="inlineStr"/>
+      <c r="H52" s="11" t="inlineStr"/>
+      <c r="I52" s="11" t="inlineStr"/>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
+      <c r="L52" s="11" t="inlineStr"/>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N52" s="11" t="inlineStr"/>
+      <c r="O52" s="11" t="inlineStr"/>
+      <c r="P52" s="11" t="inlineStr"/>
+      <c r="Q52" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R52" s="11" t="inlineStr"/>
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
+      <c r="U52" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V52" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W52" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>20260583021</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr"/>
+      <c r="H53" s="11" t="inlineStr"/>
+      <c r="I53" s="11" t="inlineStr"/>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr"/>
+      <c r="L53" s="11" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N53" s="11" t="inlineStr"/>
+      <c r="O53" s="11" t="inlineStr"/>
+      <c r="P53" s="11" t="inlineStr"/>
+      <c r="Q53" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R53" s="11" t="inlineStr"/>
+      <c r="S53" s="11" t="inlineStr">
+        <is>
+          <t>103-49-023</t>
+        </is>
+      </c>
+      <c r="T53" s="11" t="inlineStr"/>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V53" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>20260584064</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr"/>
+      <c r="I54" s="11" t="inlineStr"/>
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr"/>
+      <c r="L54" s="11" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr"/>
+      <c r="O54" s="11" t="inlineStr"/>
+      <c r="P54" s="11" t="inlineStr"/>
+      <c r="Q54" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R54" s="11" t="inlineStr"/>
+      <c r="S54" s="11" t="inlineStr"/>
+      <c r="T54" s="11" t="inlineStr"/>
+      <c r="U54" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V54" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W54" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>20260584065</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr"/>
+      <c r="I55" s="11" t="inlineStr"/>
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr"/>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N55" s="11" t="inlineStr"/>
+      <c r="O55" s="11" t="inlineStr"/>
+      <c r="P55" s="11" t="inlineStr"/>
+      <c r="Q55" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R55" s="11" t="inlineStr"/>
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
+      <c r="U55" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V55" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W55" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>20260584066</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr"/>
+      <c r="G56" s="11" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr"/>
+      <c r="I56" s="11" t="inlineStr"/>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr"/>
+      <c r="L56" s="11" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N56" s="11" t="inlineStr"/>
+      <c r="O56" s="11" t="inlineStr"/>
+      <c r="P56" s="11" t="inlineStr"/>
+      <c r="Q56" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R56" s="11" t="inlineStr"/>
+      <c r="S56" s="11" t="inlineStr"/>
+      <c r="T56" s="11" t="inlineStr"/>
+      <c r="U56" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V56" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W56" s="12" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W6"/>
+  <autoFilter ref="A1:W56"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -982,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -990,7 +4921,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -999,98 +4930,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-07 06:57</t>
+          <t>Run: 2026-10-08 07:01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr"/>
+      <c r="A3" s="14" t="inlineStr"/>
+      <c r="B3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>5</v>
+      <c r="B4" s="14" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>With Property Address</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="14" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>With Mailing Address</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>With Mailing Address</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>PDF Parsed</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>5</v>
+      <c r="B7" s="14" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Score 70+ (Hot)</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>0</v>
+      <c r="B8" s="14" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Score 50-69 (Warm)</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>0</v>
+      <c r="B9" s="14" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr"/>
+      <c r="A10" s="14" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>By Category</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Tax Deed</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>5</v>
+      <c r="B14" s="14" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-11 06:56</t>
+          <t>Run: 2026-10-12 07:04</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,22 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00374151"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
@@ -49,7 +65,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +75,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2433"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,14 +109,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -606,8 +636,3138 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>20260596476</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>20260596477</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>20260596478</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>20260596479</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>20260596480</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>20260596495</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>20260596599</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>20260596600</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>20260596601</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>20260596602</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>20260596603</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>20260596604</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>20260596605</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>20260596606</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>20260596652</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>20260596666</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>20260596679</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>20260596680</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>20260596681</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>20260594202</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>20260594204</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>20260594205</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>20260594206</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>20260594207</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>20260594208</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>20260594705</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>20260594706</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>20260594707</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>20260594708</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>20260594709</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>20260594710</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>20260595292</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Case No. CV2026-016437</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>20260595465</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>20260595605</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>20260596536</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>20260596558</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>20260596559</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>20260596561</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>20260595461</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>20260595764</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>20260594432</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr"/>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>155-53-067</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>20260594509</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>20260595585</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>20260595640</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W45" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>20260595922</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>20260596416</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W47" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>20260596463</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W48" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>20260596699</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr"/>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W49" s="4" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W49"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -618,7 +3778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -626,7 +3786,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -635,88 +3795,128 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-14 05:55</t>
+          <t>Run: 2026-10-15 05:38</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="A3" s="6" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>With Property Address</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>With Property Address</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>With Mailing Address</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>With Mailing Address</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>PDF Parsed</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Score 70+ (Hot)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>PDF Parsed</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Score 50-69 (Warm)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Score 70+ (Hot)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Score 50-69 (Warm)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>By Category</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-16 05:33</t>
+          <t>Run: 2026-10-17 05:26</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-17 05:26</t>
+          <t>Run: 2026-10-18 05:31</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-18 05:31</t>
+          <t>Run: 2026-10-19 05:47</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-19 05:47</t>
+          <t>Run: 2026-10-20 05:50</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-20 05:50</t>
+          <t>Run: 2026-10-21 05:50</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-21 05:50</t>
+          <t>Run: 2026-10-22 05:53</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-22 05:53</t>
+          <t>Run: 2026-10-23 05:53</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-23 05:53</t>
+          <t>Run: 2026-10-24 05:30</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-24 05:30</t>
+          <t>Run: 2026-10-25 05:47</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-25 05:47</t>
+          <t>Run: 2026-10-26 05:53</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-26 05:53</t>
+          <t>Run: 2026-10-27 06:04</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-27 06:04</t>
+          <t>Run: 2026-10-28 06:44</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-28 06:44</t>
+          <t>Run: 2026-10-29 06:53</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-29 06:53</t>
+          <t>Run: 2026-10-30 06:55</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-10-30 06:55</t>
+          <t>Run: 2026-10-31 06:45</t>
         </is>
       </c>
     </row>
